--- a/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_35.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.2/Output_12_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2036747.63227795</v>
+        <v>2037818.755990224</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.8203195</v>
+        <v>14697842.82031941</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.8203195</v>
+        <v>14697842.82031941</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984940391</v>
+        <v>657188.6984939944</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984940391</v>
+        <v>657188.6984939944</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31155692.28278469</v>
+        <v>31155692.28278466</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
         <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
-        <v>1.79868786782652</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.798687867826661</v>
       </c>
       <c r="S2" t="n">
         <v>85.50414770182039</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -742,7 +742,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>339.6362423378769</v>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>41.78759548455745</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
-        <v>374</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
         <v>4.473444462796863</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>321.970881421104</v>
       </c>
     </row>
     <row r="4">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -982,16 +982,16 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>9.350829326972454</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,13 +1015,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
         <v>133.6519859716245</v>
       </c>
       <c r="S6" t="n">
-        <v>374</v>
+        <v>62.48881128536601</v>
       </c>
       <c r="T6" t="n">
         <v>4.473444462796863</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>349.410409898671</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1146,7 +1146,7 @@
         <v>3.34732203575993</v>
       </c>
       <c r="H8" t="n">
-        <v>3.81023156784903</v>
+        <v>5.608919435675552</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1176,7 +1176,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>85.50414770182039</v>
@@ -1210,10 +1210,10 @@
         <v>374</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>71.58074055488464</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>78.54339244579138</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1273,7 +1273,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>374</v>
       </c>
       <c r="Y9" t="n">
         <v>374</v>
@@ -1374,7 +1374,7 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E11" t="n">
-        <v>84.66720461043069</v>
+        <v>85.36328960686865</v>
       </c>
       <c r="F11" t="n">
         <v>85.88962870801186</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>142.2280170485541</v>
+        <v>141.5319320520589</v>
       </c>
       <c r="T11" t="n">
         <v>261.2171194170061</v>
@@ -1450,7 +1450,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>61.9323473515352</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E12" t="n">
         <v>23.67209722191262</v>
@@ -1465,7 +1465,7 @@
         <v>5.544181526043758</v>
       </c>
       <c r="I12" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S12" t="n">
-        <v>132.901311285366</v>
+        <v>355.8435840456418</v>
       </c>
       <c r="T12" t="n">
-        <v>402.1759444627968</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U12" t="n">
         <v>81.15842579792258</v>
@@ -1510,7 +1510,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y12" t="n">
         <v>80.39139276613435</v>
@@ -1562,13 +1562,13 @@
         <v>150.9111244520127</v>
       </c>
       <c r="O13" t="n">
-        <v>227.9026788331133</v>
+        <v>225.052317355647</v>
       </c>
       <c r="P13" t="n">
         <v>288.4057989676218</v>
       </c>
       <c r="Q13" t="n">
-        <v>348.5719049481314</v>
+        <v>351.422266425598</v>
       </c>
       <c r="R13" t="n">
         <v>377.8450460139379</v>
@@ -1617,7 +1617,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H14" t="n">
         <v>73.89995518593948</v>
@@ -1665,7 +1665,7 @@
         <v>310.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>318.6773909845096</v>
+        <v>319.3734759809475</v>
       </c>
       <c r="X14" t="n">
         <v>273.2818334606677</v>
@@ -1681,22 +1681,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>288.498829406602</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C15" t="n">
         <v>42.09991244551929</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F15" t="n">
         <v>20.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>5.950139648612248</v>
+        <v>228.8924124088879</v>
       </c>
       <c r="H15" t="n">
         <v>5.544181526043773</v>
@@ -1750,7 +1750,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>80.39139276613435</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1811,7 +1811,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S16" t="n">
-        <v>28.98969199588108</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>82.5859104061561</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H17" t="n">
-        <v>73.89995518593948</v>
+        <v>73.2038701894446</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>65.55655664632661</v>
+        <v>288.4988294066023</v>
       </c>
       <c r="C18" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E18" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H18" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1963,28 +1963,28 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S18" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T18" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U18" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V18" t="n">
-        <v>246.1394107103725</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>113.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y18" t="n">
         <v>80.39139276613435</v>
@@ -2027,16 +2027,16 @@
         <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M19" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N19" t="n">
         <v>150.9111244520127</v>
       </c>
       <c r="O19" t="n">
-        <v>227.9026788331133</v>
+        <v>225.052317355647</v>
       </c>
       <c r="P19" t="n">
         <v>288.4057989676218</v>
@@ -2045,10 +2045,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>28.98969199588153</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,7 +2091,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>82.5859104061561</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H20" t="n">
         <v>73.89995518593948</v>
@@ -2139,7 +2139,7 @@
         <v>310.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>319.3734759809475</v>
+        <v>318.6773909844526</v>
       </c>
       <c r="X20" t="n">
         <v>273.2818334606677</v>
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>288.4988294066021</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C21" t="n">
         <v>42.09991244551929</v>
@@ -2218,7 +2218,7 @@
         <v>95.51066719152016</v>
       </c>
       <c r="W21" t="n">
-        <v>432.3731429098285</v>
+        <v>336.3154156701044</v>
       </c>
       <c r="X21" t="n">
         <v>419.8627394453875</v>
@@ -2285,7 +2285,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>28.98969199588108</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G23" t="n">
-        <v>83.28199540259408</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H23" t="n">
         <v>73.89995518593946</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>141.531932052116</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2395,16 +2395,16 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>42.09991244551929</v>
+        <v>265.042185205795</v>
       </c>
       <c r="D24" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G24" t="n">
         <v>5.950139648612264</v>
@@ -2449,16 +2449,16 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V24" t="n">
-        <v>318.4529399517954</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W24" t="n">
         <v>113.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y24" t="n">
         <v>80.39139276613435</v>
@@ -2519,10 +2519,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>374.9946845364714</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2562,13 +2562,13 @@
         <v>85.36328960686865</v>
       </c>
       <c r="F26" t="n">
-        <v>85.19354371154385</v>
+        <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
         <v>83.28199540259411</v>
       </c>
       <c r="H26" t="n">
-        <v>73.89995518593948</v>
+        <v>73.20387018952971</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2635,7 +2635,7 @@
         <v>42.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -2644,10 +2644,10 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043773</v>
+        <v>228.4864542863189</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2695,7 +2695,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X27" t="n">
-        <v>323.8050122056632</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y27" t="n">
         <v>80.39139276613435</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.305168319657323</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M28" t="n">
         <v>97.89093927140236</v>
@@ -2756,7 +2756,7 @@
         <v>351.422266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364717</v>
       </c>
       <c r="S28" t="n">
         <v>31.84005347334724</v>
@@ -2802,7 +2802,7 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>82.58591040612612</v>
+        <v>82.58591040614833</v>
       </c>
       <c r="H29" t="n">
         <v>73.89995518593946</v>
@@ -2872,10 +2872,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D30" t="n">
-        <v>28.93768689770263</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
         <v>20.63624233787687</v>
@@ -2884,7 +2884,7 @@
         <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043758</v>
+        <v>228.4864542863191</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2923,16 +2923,16 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>304.1006985581982</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>419.8627394453875</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y30" t="n">
         <v>80.39139276613435</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6.155529797123449</v>
+        <v>3.305168319656647</v>
       </c>
       <c r="M31" t="n">
         <v>97.89093927140237</v>
@@ -2990,7 +2990,7 @@
         <v>288.4057989676218</v>
       </c>
       <c r="Q31" t="n">
-        <v>348.5719049481315</v>
+        <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
         <v>377.8450460139379</v>
@@ -3039,10 +3039,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G32" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040618435</v>
       </c>
       <c r="H32" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3072,10 +3072,10 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-8.823917596600949e-11</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>141.5319320521741</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T32" t="n">
         <v>261.2171194170061</v>
@@ -3103,25 +3103,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>65.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C33" t="n">
-        <v>42.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
         <v>28.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>243.5785150981523</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H33" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I33" t="n">
         <v>0</v>
@@ -3151,25 +3151,25 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>498.2619859716245</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S33" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T33" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U33" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V33" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W33" t="n">
-        <v>113.3731429098285</v>
+        <v>336.3154156701039</v>
       </c>
       <c r="X33" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y33" t="n">
         <v>80.39139276613435</v>
@@ -3212,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M34" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N34" t="n">
         <v>150.9111244520127</v>
@@ -3224,16 +3224,16 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P34" t="n">
-        <v>285.5554374901557</v>
+        <v>288.4057989676218</v>
       </c>
       <c r="Q34" t="n">
         <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364713</v>
       </c>
       <c r="S34" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3273,10 +3273,10 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F35" t="n">
-        <v>4.588698897426238</v>
+        <v>7.889628708011855</v>
       </c>
       <c r="G35" t="n">
-        <v>5.2819954025941</v>
+        <v>5.281995402594077</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>64.22801704855405</v>
+        <v>60.92708723808357</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
@@ -3346,10 +3346,10 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
         <v>339.6362423378769</v>
@@ -3388,25 +3388,25 @@
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>101.2619859716246</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S36" t="n">
-        <v>54.90131128536602</v>
+        <v>233.4388749973786</v>
       </c>
       <c r="T36" t="n">
-        <v>5.175944462796835</v>
+        <v>5.175944462796849</v>
       </c>
       <c r="U36" t="n">
-        <v>3.158425797922597</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V36" t="n">
-        <v>196.8938973783651</v>
+        <v>17.51066719152016</v>
       </c>
       <c r="W36" t="n">
-        <v>374.0000000000364</v>
+        <v>35.37314290982852</v>
       </c>
       <c r="X36" t="n">
-        <v>374.0000000000364</v>
+        <v>22.86273944538755</v>
       </c>
       <c r="Y36" t="n">
         <v>2.391392766134345</v>
@@ -3452,10 +3452,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>19.89093927140236</v>
+        <v>19.89093927140237</v>
       </c>
       <c r="N37" t="n">
-        <v>72.91112445201273</v>
+        <v>72.9111244520127</v>
       </c>
       <c r="O37" t="n">
         <v>149.9026788331133</v>
@@ -3467,7 +3467,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>299.845046013938</v>
+        <v>299.8450460139379</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
-        <v>4.588698897426238</v>
+        <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
         <v>5.2819954025941</v>
@@ -3555,7 +3555,7 @@
         <v>183.2171194170061</v>
       </c>
       <c r="U38" t="n">
-        <v>252.1032663978569</v>
+        <v>248.8023365873864</v>
       </c>
       <c r="V38" t="n">
         <v>232.8510241668239</v>
@@ -3583,19 +3583,19 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>184.5126391075911</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>84.76036436294697</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>324.5441815260438</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R39" t="n">
         <v>101.2619859716246</v>
@@ -3640,7 +3640,7 @@
         <v>17.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>374.0000000000637</v>
+        <v>35.37314290982852</v>
       </c>
       <c r="X39" t="n">
         <v>22.86273944538755</v>
@@ -3735,16 +3735,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>156.4745782429939</v>
+        <v>112.2300255030828</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -3753,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>99.89995518593948</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3786,10 +3786,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>168.2280170485541</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>234.4232955120103</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>218.3174326828064</v>
@@ -3862,7 +3862,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>207.6487594170198</v>
+        <v>207.6487594171348</v>
       </c>
       <c r="S42" t="n">
         <v>158.901311285366</v>
@@ -3923,25 +3923,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712344</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>87.74326712526162</v>
+        <v>2.581873503823019</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
         <v>253.9026788331133</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>374.0000000006022</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>374.0000000005899</v>
+        <v>374.0000000001201</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>188.9993129555745</v>
+        <v>139.277699471613</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>44.42220027913408</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -3990,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>99.89995518593946</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4032,13 +4032,13 @@
         <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -4066,13 +4066,13 @@
         <v>46.63624233787687</v>
       </c>
       <c r="G45" t="n">
-        <v>31.95013964861226</v>
+        <v>31.95013964861225</v>
       </c>
       <c r="H45" t="n">
-        <v>31.54418152604376</v>
+        <v>31.54418152604377</v>
       </c>
       <c r="I45" t="n">
-        <v>2.386773445395086</v>
+        <v>2.386773445510338</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,7 +4099,7 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>205.2619859716245</v>
+        <v>205.2619859716246</v>
       </c>
       <c r="S45" t="n">
         <v>158.901311285366</v>
@@ -4160,28 +4160,28 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>32.15552979712345</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>166.4889690665931</v>
+        <v>1.555623315292362</v>
       </c>
       <c r="P46" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>373.9999999999923</v>
+        <v>374.0000000002147</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>374.0000000002147</v>
       </c>
       <c r="S46" t="n">
-        <v>57.84005347334727</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T46" t="n">
         <v>0</v>
@@ -4297,40 +4297,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>108.731003807232</v>
+        <v>106.914147375084</v>
       </c>
       <c r="C2" t="n">
-        <v>58.7566823496624</v>
+        <v>56.9398259175144</v>
       </c>
       <c r="D2" t="n">
-        <v>48.31309069324847</v>
+        <v>46.49623426110047</v>
       </c>
       <c r="E2" t="n">
-        <v>43.90572745398721</v>
+        <v>42.08887102183921</v>
       </c>
       <c r="F2" t="n">
-        <v>38.96670855700554</v>
+        <v>37.14985212485754</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
-        <v>31.736856432148</v>
+        <v>29.92</v>
       </c>
       <c r="I2" t="n">
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>29.92</v>
+        <v>211.4278628071088</v>
       </c>
       <c r="K2" t="n">
-        <v>400.18</v>
+        <v>263.0661931588676</v>
       </c>
       <c r="L2" t="n">
+        <v>327.128108133742</v>
+      </c>
+      <c r="M2" t="n">
         <v>697.388108133742</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1067.648108133742</v>
       </c>
       <c r="N2" t="n">
         <v>1067.648108133742</v>
@@ -4345,28 +4345,28 @@
         <v>1496</v>
       </c>
       <c r="R2" t="n">
-        <v>1496</v>
+        <v>1494.183143567852</v>
       </c>
       <c r="S2" t="n">
-        <v>1409.632174038565</v>
+        <v>1407.815317606417</v>
       </c>
       <c r="T2" t="n">
-        <v>1222.884106610596</v>
+        <v>1221.067250178448</v>
       </c>
       <c r="U2" t="n">
-        <v>971.1785586019998</v>
+        <v>969.3617021698518</v>
       </c>
       <c r="V2" t="n">
-        <v>739.0058069183393</v>
+        <v>737.1889504861913</v>
       </c>
       <c r="W2" t="n">
-        <v>498.2245180486953</v>
+        <v>496.4076616165473</v>
       </c>
       <c r="X2" t="n">
-        <v>304.0004438460006</v>
+        <v>302.1835874138526</v>
       </c>
       <c r="Y2" t="n">
-        <v>191.5585926512467</v>
+        <v>189.7417362190987</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>764.5440050297947</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="C3" t="n">
-        <v>764.5440050297947</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="D3" t="n">
-        <v>764.5440050297947</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="E3" t="n">
-        <v>418.4105734925092</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="F3" t="n">
-        <v>75.34366204010826</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="G3" t="n">
-        <v>75.34366204010826</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="H3" t="n">
-        <v>75.34366204010826</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4427,25 +4427,25 @@
         <v>1214.459075542376</v>
       </c>
       <c r="S3" t="n">
-        <v>836.6812977645984</v>
+        <v>1151.339064143017</v>
       </c>
       <c r="T3" t="n">
-        <v>832.1626669940965</v>
+        <v>1146.820433372515</v>
       </c>
       <c r="U3" t="n">
-        <v>831.9647621477101</v>
+        <v>1146.622528526128</v>
       </c>
       <c r="V3" t="n">
-        <v>817.307522560316</v>
+        <v>1131.965288938734</v>
       </c>
       <c r="W3" t="n">
-        <v>784.6073782069539</v>
+        <v>1099.265144585372</v>
       </c>
       <c r="X3" t="n">
-        <v>764.5440050297947</v>
+        <v>1079.201771408213</v>
       </c>
       <c r="Y3" t="n">
-        <v>764.5440050297947</v>
+        <v>753.9786588616431</v>
       </c>
     </row>
     <row r="4">
@@ -4455,22 +4455,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>693.8274288950204</v>
+        <v>1018.551665842943</v>
       </c>
       <c r="C4" t="n">
-        <v>819.8294347134562</v>
+        <v>1144.553671661379</v>
       </c>
       <c r="D4" t="n">
-        <v>819.8294347134562</v>
+        <v>1144.553671661379</v>
       </c>
       <c r="E4" t="n">
-        <v>937.6583389248692</v>
+        <v>1262.382575872791</v>
       </c>
       <c r="F4" t="n">
-        <v>1062.019311516805</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="G4" t="n">
-        <v>1215.607972485657</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="H4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>60.67502604617124</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T4" t="n">
-        <v>60.67502604617124</v>
+        <v>250.2474385758229</v>
       </c>
       <c r="U4" t="n">
-        <v>60.67502604617124</v>
+        <v>496.8085636731259</v>
       </c>
       <c r="V4" t="n">
-        <v>259.4964189321172</v>
+        <v>695.6299565590718</v>
       </c>
       <c r="W4" t="n">
-        <v>431.3873371917946</v>
+        <v>867.5208748187492</v>
       </c>
       <c r="X4" t="n">
-        <v>582.4181282159881</v>
+        <v>1018.551665842943</v>
       </c>
       <c r="Y4" t="n">
-        <v>693.8274288950204</v>
+        <v>1018.551665842943</v>
       </c>
     </row>
     <row r="5">
@@ -4558,25 +4558,25 @@
         <v>29.92</v>
       </c>
       <c r="J5" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="K5" t="n">
         <v>400.18</v>
       </c>
-      <c r="K5" t="n">
-        <v>770.4399999999999</v>
-      </c>
       <c r="L5" t="n">
-        <v>834.5019149748742</v>
+        <v>697.388108133742</v>
       </c>
       <c r="M5" t="n">
-        <v>834.5019149748744</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="N5" t="n">
-        <v>834.5019149748744</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="O5" t="n">
-        <v>834.5019149748744</v>
+        <v>1437.908108133742</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>574.9925190227137</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="C6" t="n">
-        <v>574.9925190227137</v>
+        <v>711.2404154681431</v>
       </c>
       <c r="D6" t="n">
-        <v>574.9925190227137</v>
+        <v>711.2404154681431</v>
       </c>
       <c r="E6" t="n">
-        <v>574.9925190227137</v>
+        <v>711.2404154681431</v>
       </c>
       <c r="F6" t="n">
-        <v>574.9925190227137</v>
+        <v>368.1735040157421</v>
       </c>
       <c r="G6" t="n">
-        <v>574.9925190227137</v>
+        <v>39.36528214845703</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>39.36528214845703</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1492.786030368536</v>
+        <v>1346.247111942856</v>
       </c>
       <c r="R6" t="n">
-        <v>1357.784024336592</v>
+        <v>1211.245105910912</v>
       </c>
       <c r="S6" t="n">
-        <v>980.0062465588139</v>
+        <v>1148.125094511552</v>
       </c>
       <c r="T6" t="n">
-        <v>975.487615788312</v>
+        <v>1143.60646374105</v>
       </c>
       <c r="U6" t="n">
-        <v>975.2897109419256</v>
+        <v>1143.408558894664</v>
       </c>
       <c r="V6" t="n">
-        <v>960.6324713545315</v>
+        <v>1128.75131930727</v>
       </c>
       <c r="W6" t="n">
-        <v>927.9323270011694</v>
+        <v>1096.051174953908</v>
       </c>
       <c r="X6" t="n">
-        <v>574.9925190227137</v>
+        <v>1075.987801776748</v>
       </c>
       <c r="Y6" t="n">
-        <v>574.9925190227137</v>
+        <v>1075.987801776748</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>363.8369457388728</v>
+        <v>182.101013416203</v>
       </c>
       <c r="C7" t="n">
-        <v>489.8389515573086</v>
+        <v>308.1030192346387</v>
       </c>
       <c r="D7" t="n">
-        <v>603.1580956823087</v>
+        <v>421.4221633596388</v>
       </c>
       <c r="E7" t="n">
-        <v>720.9869998937218</v>
+        <v>539.2510675710519</v>
       </c>
       <c r="F7" t="n">
-        <v>845.3479724856572</v>
+        <v>663.6120401629873</v>
       </c>
       <c r="G7" t="n">
-        <v>845.3479724856572</v>
+        <v>817.2007011318399</v>
       </c>
       <c r="H7" t="n">
-        <v>1016.483548464727</v>
+        <v>988.3362771109096</v>
       </c>
       <c r="I7" t="n">
-        <v>1016.483548464727</v>
+        <v>1214.945251784697</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="U7" t="n">
-        <v>252.0796080725807</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="V7" t="n">
-        <v>252.0796080725807</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="W7" t="n">
-        <v>252.0796080725807</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="X7" t="n">
-        <v>252.0796080725807</v>
+        <v>70.34367574991084</v>
       </c>
       <c r="Y7" t="n">
-        <v>252.0796080725807</v>
+        <v>70.34367574991084</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106.914147375084</v>
+        <v>108.731003807232</v>
       </c>
       <c r="C8" t="n">
-        <v>56.9398259175144</v>
+        <v>58.7566823496624</v>
       </c>
       <c r="D8" t="n">
-        <v>46.49623426110047</v>
+        <v>48.31309069324847</v>
       </c>
       <c r="E8" t="n">
-        <v>42.08887102183921</v>
+        <v>43.90572745398721</v>
       </c>
       <c r="F8" t="n">
-        <v>37.14985212485754</v>
+        <v>38.96670855700554</v>
       </c>
       <c r="G8" t="n">
-        <v>33.76871875540306</v>
+        <v>35.58557518755106</v>
       </c>
       <c r="H8" t="n">
         <v>29.92</v>
@@ -4798,19 +4798,19 @@
         <v>29.92</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L8" t="n">
-        <v>464.2419149748744</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M8" t="n">
-        <v>834.5019149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="N8" t="n">
-        <v>834.5019149748744</v>
+        <v>886.1402453266331</v>
       </c>
       <c r="O8" t="n">
-        <v>834.5019149748744</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
         <v>1125.74</v>
@@ -4819,28 +4819,28 @@
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.183143567852</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
-        <v>1407.815317606417</v>
+        <v>1409.632174038565</v>
       </c>
       <c r="T8" t="n">
-        <v>1221.067250178448</v>
+        <v>1222.884106610596</v>
       </c>
       <c r="U8" t="n">
-        <v>969.3617021698518</v>
+        <v>971.1785586019998</v>
       </c>
       <c r="V8" t="n">
-        <v>737.1889504861913</v>
+        <v>739.0058069183393</v>
       </c>
       <c r="W8" t="n">
-        <v>496.4076616165473</v>
+        <v>498.2245180486953</v>
       </c>
       <c r="X8" t="n">
-        <v>302.1835874138526</v>
+        <v>304.0004438460006</v>
       </c>
       <c r="Y8" t="n">
-        <v>189.7417362190987</v>
+        <v>191.5585926512467</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>466.9711646468727</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="C9" t="n">
-        <v>102.2237783382673</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="D9" t="n">
-        <v>29.92</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="E9" t="n">
-        <v>29.92</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="F9" t="n">
-        <v>29.92</v>
+        <v>109.2567600462539</v>
       </c>
       <c r="G9" t="n">
         <v>29.92</v>
@@ -4916,10 +4916,10 @@
         <v>1242.590093379587</v>
       </c>
       <c r="X9" t="n">
-        <v>1222.526720202428</v>
+        <v>864.8123156018096</v>
       </c>
       <c r="Y9" t="n">
-        <v>844.7489424246505</v>
+        <v>487.0345378240318</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>822.5694727264984</v>
+        <v>580.5082847700203</v>
       </c>
       <c r="C10" t="n">
-        <v>948.5714785449342</v>
+        <v>706.5102905884561</v>
       </c>
       <c r="D10" t="n">
-        <v>948.5714785449342</v>
+        <v>819.8294347134562</v>
       </c>
       <c r="E10" t="n">
-        <v>1066.400382756347</v>
+        <v>937.6583389248692</v>
       </c>
       <c r="F10" t="n">
-        <v>1066.400382756347</v>
+        <v>1062.019311516805</v>
       </c>
       <c r="G10" t="n">
-        <v>1066.400382756347</v>
+        <v>1215.607972485657</v>
       </c>
       <c r="H10" t="n">
-        <v>1066.400382756347</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="I10" t="n">
-        <v>1066.400382756347</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="J10" t="n">
         <v>1386.743548464727</v>
@@ -4986,19 +4986,19 @@
         <v>29.92</v>
       </c>
       <c r="U10" t="n">
-        <v>276.481125097303</v>
+        <v>29.92</v>
       </c>
       <c r="V10" t="n">
-        <v>276.481125097303</v>
+        <v>34.41993714082497</v>
       </c>
       <c r="W10" t="n">
-        <v>448.3720433569805</v>
+        <v>206.3108554005024</v>
       </c>
       <c r="X10" t="n">
-        <v>599.402834381174</v>
+        <v>357.3416464246959</v>
       </c>
       <c r="Y10" t="n">
-        <v>710.8121350602063</v>
+        <v>468.7509471037282</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>607.5035534240616</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C11" t="n">
-        <v>475.7110501483102</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D11" t="n">
-        <v>383.4492766737144</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E11" t="n">
-        <v>297.9268477742895</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F11" t="n">
-        <v>211.169647059126</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G11" t="n">
-        <v>127.046419379738</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H11" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I11" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>141.6759849731407</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K11" t="n">
-        <v>327.4727226113316</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L11" t="n">
-        <v>557.9700049228894</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M11" t="n">
-        <v>1113.344759641309</v>
+        <v>988.9116280297777</v>
       </c>
       <c r="N11" t="n">
-        <v>1761.794759641324</v>
+        <v>1637.361628029778</v>
       </c>
       <c r="O11" t="n">
-        <v>2410.244759641338</v>
+        <v>1813.91480011625</v>
       </c>
       <c r="P11" t="n">
-        <v>2620.000000000059</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q11" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="R11" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="S11" t="n">
-        <v>2476.335336314651</v>
+        <v>2477.038452472668</v>
       </c>
       <c r="T11" t="n">
-        <v>2212.479660135857</v>
+        <v>2213.182776293874</v>
       </c>
       <c r="U11" t="n">
-        <v>1879.042017309739</v>
+        <v>1879.745133467756</v>
       </c>
       <c r="V11" t="n">
-        <v>1565.051083807896</v>
+        <v>1565.754199965913</v>
       </c>
       <c r="W11" t="n">
-        <v>1242.45161312007</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X11" t="n">
-        <v>966.4093570991938</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y11" t="n">
-        <v>772.149324086258</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>727.9379119575193</v>
+        <v>824.9659192703712</v>
       </c>
       <c r="C12" t="n">
-        <v>363.1905256489139</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D12" t="n">
-        <v>300.6325990312016</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E12" t="n">
-        <v>276.7213897161383</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F12" t="n">
-        <v>255.8767004859597</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G12" t="n">
-        <v>249.8664584166544</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H12" t="n">
-        <v>244.2662750570142</v>
+        <v>52.4</v>
       </c>
       <c r="I12" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J12" t="n">
-        <v>250.1913459300171</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K12" t="n">
-        <v>565.5796394772308</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L12" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M12" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N12" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O12" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P12" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q12" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R12" t="n">
-        <v>2132.917892265886</v>
+        <v>1810.695670043663</v>
       </c>
       <c r="S12" t="n">
-        <v>1998.674143492789</v>
+        <v>1451.257706361196</v>
       </c>
       <c r="T12" t="n">
-        <v>1592.43581575259</v>
+        <v>1367.241600843219</v>
       </c>
       <c r="U12" t="n">
-        <v>1510.4576078759</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V12" t="n">
-        <v>1413.982186470324</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W12" t="n">
-        <v>1299.46386029878</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X12" t="n">
-        <v>875.3600830812172</v>
+        <v>972.3880903940691</v>
       </c>
       <c r="Y12" t="n">
-        <v>794.1566560447179</v>
+        <v>891.1846633575698</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>673.4417775581356</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C13" t="n">
-        <v>719.2537833765714</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D13" t="n">
-        <v>752.3829275015714</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E13" t="n">
-        <v>790.0218317129844</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F13" t="n">
-        <v>834.1928043049199</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G13" t="n">
-        <v>908.0645554377069</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H13" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I13" t="n">
         <v>1163.862419205318</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K13" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L13" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M13" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N13" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O13" t="n">
-        <v>1109.635154952565</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P13" t="n">
-        <v>818.3161660963816</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q13" t="n">
-        <v>466.2233328154408</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R13" t="n">
-        <v>84.56167017509942</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S13" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="T13" t="n">
-        <v>163.0851070276585</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U13" t="n">
-        <v>329.4820370429943</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V13" t="n">
-        <v>448.1134299289403</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W13" t="n">
-        <v>539.8143481886177</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X13" t="n">
-        <v>610.6551392128113</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y13" t="n">
-        <v>641.8744398918435</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>608.2066695820798</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C14" t="n">
-        <v>476.4141663063284</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D14" t="n">
-        <v>384.1523928317326</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E14" t="n">
-        <v>297.9268477742895</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F14" t="n">
-        <v>211.169647059126</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G14" t="n">
-        <v>127.046419379738</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H14" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I14" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J14" t="n">
-        <v>141.6759849731407</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K14" t="n">
-        <v>327.4727226113316</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L14" t="n">
-        <v>674.6500000000154</v>
+        <v>1020.623267284697</v>
       </c>
       <c r="M14" t="n">
-        <v>1323.10000000003</v>
+        <v>1669.073267284698</v>
       </c>
       <c r="N14" t="n">
-        <v>1323.10000000003</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O14" t="n">
-        <v>1971.550000000044</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P14" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="Q14" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="R14" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="S14" t="n">
-        <v>2476.335336314651</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T14" t="n">
-        <v>2212.479660135857</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U14" t="n">
-        <v>1879.042017309739</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V14" t="n">
-        <v>1565.051083807896</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W14" t="n">
-        <v>1243.154729278089</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X14" t="n">
-        <v>967.1124732572121</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y14" t="n">
-        <v>772.8524402442763</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>824.9659192703724</v>
+        <v>405.7156897352961</v>
       </c>
       <c r="C15" t="n">
-        <v>782.4407551839893</v>
+        <v>363.1905256489129</v>
       </c>
       <c r="D15" t="n">
-        <v>430.9885461964108</v>
+        <v>333.9605388835567</v>
       </c>
       <c r="E15" t="n">
-        <v>84.85511465912529</v>
+        <v>310.0493295684934</v>
       </c>
       <c r="F15" t="n">
-        <v>64.01042542894665</v>
+        <v>289.2046403383148</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964135</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H15" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I15" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J15" t="n">
-        <v>250.1913459300171</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K15" t="n">
-        <v>565.5796394772308</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L15" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M15" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N15" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P15" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q15" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R15" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S15" t="n">
-        <v>1998.674143492789</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T15" t="n">
-        <v>1914.658037974812</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U15" t="n">
         <v>1832.679830098122</v>
       </c>
       <c r="V15" t="n">
-        <v>1736.204408692547</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W15" t="n">
-        <v>1621.686082521003</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X15" t="n">
-        <v>1197.582305303439</v>
+        <v>1197.582305303438</v>
       </c>
       <c r="Y15" t="n">
-        <v>1116.37887826694</v>
+        <v>794.1566560447169</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>673.4417775581356</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C16" t="n">
-        <v>719.2537833765714</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D16" t="n">
-        <v>752.3829275015714</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E16" t="n">
-        <v>790.0218317129844</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F16" t="n">
-        <v>834.1928043049199</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G16" t="n">
-        <v>908.0645554377069</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H16" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I16" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J16" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K16" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N16" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O16" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P16" t="n">
-        <v>818.3161660963821</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.3441798078993</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R16" t="n">
-        <v>81.68251716755782</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S16" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="T16" t="n">
-        <v>163.0851070276585</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U16" t="n">
-        <v>329.4820370429943</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V16" t="n">
-        <v>448.1134299289403</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W16" t="n">
-        <v>539.8143481886177</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X16" t="n">
-        <v>610.6551392128113</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y16" t="n">
-        <v>641.8744398918435</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>607.5035534240616</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C17" t="n">
-        <v>475.7110501483102</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D17" t="n">
-        <v>383.4492766737144</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E17" t="n">
-        <v>297.2237316162713</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F17" t="n">
-        <v>210.4665309011078</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G17" t="n">
-        <v>127.046419379738</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H17" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I17" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J17" t="n">
-        <v>141.6759849731407</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K17" t="n">
-        <v>790.1259849731551</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L17" t="n">
-        <v>1020.623267284713</v>
+        <v>936.7915875548047</v>
       </c>
       <c r="M17" t="n">
-        <v>1585.241587554851</v>
+        <v>1585.241587554806</v>
       </c>
       <c r="N17" t="n">
-        <v>2233.691587554866</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O17" t="n">
-        <v>2410.244759641338</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P17" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="Q17" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="R17" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="S17" t="n">
-        <v>2476.335336314651</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T17" t="n">
-        <v>2212.479660135857</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U17" t="n">
-        <v>1879.042017309739</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V17" t="n">
-        <v>1565.051083807896</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W17" t="n">
-        <v>1242.45161312007</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X17" t="n">
-        <v>966.4093570991938</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y17" t="n">
-        <v>772.149324086258</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1147.188141492594</v>
+        <v>824.9659192703712</v>
       </c>
       <c r="C18" t="n">
-        <v>1104.662977406211</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D18" t="n">
-        <v>753.2107684186331</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E18" t="n">
-        <v>407.0773368813475</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F18" t="n">
-        <v>64.01042542894665</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G18" t="n">
-        <v>58.00018335964135</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H18" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I18" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J18" t="n">
-        <v>250.1913459300171</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K18" t="n">
-        <v>565.5796394772308</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L18" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M18" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N18" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O18" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P18" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q18" t="n">
-        <v>2240.946636437806</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2059.873923335155</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S18" t="n">
-        <v>1925.630174562058</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T18" t="n">
-        <v>1841.614069044082</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U18" t="n">
-        <v>1759.635861167392</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V18" t="n">
-        <v>1511.010193783177</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W18" t="n">
-        <v>1396.491867611633</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X18" t="n">
-        <v>1294.610312616292</v>
+        <v>1197.582305303438</v>
       </c>
       <c r="Y18" t="n">
-        <v>1213.406885579793</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>673.4417775581356</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C19" t="n">
-        <v>719.2537833765718</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D19" t="n">
-        <v>752.3829275015719</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E19" t="n">
-        <v>790.0218317129849</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F19" t="n">
-        <v>834.1928043049204</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G19" t="n">
-        <v>908.0645554377073</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H19" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I19" t="n">
-        <v>1163.862419205319</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J19" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K19" t="n">
-        <v>1597.372803794639</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L19" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M19" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N19" t="n">
-        <v>1339.83988104662</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O19" t="n">
-        <v>1109.635154952566</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P19" t="n">
-        <v>818.3161660963825</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.3441798078997</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R19" t="n">
-        <v>81.68251716755827</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S19" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>163.0851070276585</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U19" t="n">
-        <v>329.4820370429943</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V19" t="n">
-        <v>448.1134299289403</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W19" t="n">
-        <v>539.8143481886177</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X19" t="n">
-        <v>610.6551392128113</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y19" t="n">
-        <v>641.8744398918435</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>607.5035534240616</v>
+        <v>608.2066695820786</v>
       </c>
       <c r="C20" t="n">
-        <v>475.7110501483102</v>
+        <v>476.4141663063272</v>
       </c>
       <c r="D20" t="n">
-        <v>383.4492766737144</v>
+        <v>384.1523928317314</v>
       </c>
       <c r="E20" t="n">
-        <v>297.2237316162713</v>
+        <v>297.9268477742883</v>
       </c>
       <c r="F20" t="n">
-        <v>210.4665309011078</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G20" t="n">
-        <v>127.046419379738</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H20" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I20" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J20" t="n">
-        <v>567.6776741934357</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K20" t="n">
-        <v>1216.12767419345</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L20" t="n">
-        <v>1446.624956505008</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M20" t="n">
-        <v>1446.624956505008</v>
+        <v>1632.421694143186</v>
       </c>
       <c r="N20" t="n">
-        <v>1446.624956505008</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O20" t="n">
-        <v>1623.178128591481</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P20" t="n">
-        <v>2271.628128591481</v>
+        <v>2620</v>
       </c>
       <c r="Q20" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="R20" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2476.335336314651</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T20" t="n">
-        <v>2212.479660135857</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.042017309739</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.051083807896</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W20" t="n">
-        <v>1242.45161312007</v>
+        <v>1243.154729278087</v>
       </c>
       <c r="X20" t="n">
-        <v>966.4093570991938</v>
+        <v>967.1124732572108</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.149324086258</v>
+        <v>772.852440244275</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>180.5214748259279</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C21" t="n">
-        <v>137.9963107395448</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D21" t="n">
-        <v>108.7663239741886</v>
+        <v>108.7663239741874</v>
       </c>
       <c r="E21" t="n">
-        <v>84.85511465912529</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F21" t="n">
-        <v>64.01042542894665</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964135</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H21" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I21" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J21" t="n">
-        <v>250.1913459300171</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K21" t="n">
-        <v>565.5796394772308</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L21" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M21" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N21" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O21" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P21" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q21" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R21" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S21" t="n">
-        <v>1998.674143492789</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T21" t="n">
-        <v>1914.658037974812</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U21" t="n">
         <v>1832.679830098122</v>
       </c>
       <c r="V21" t="n">
-        <v>1736.204408692547</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W21" t="n">
-        <v>1299.46386029878</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X21" t="n">
-        <v>875.3600830812172</v>
+        <v>972.3880903940691</v>
       </c>
       <c r="Y21" t="n">
-        <v>471.9344338224956</v>
+        <v>568.9624411353475</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581356</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765714</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015714</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129844</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049199</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377069</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H22" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K22" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L22" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N22" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O22" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P22" t="n">
-        <v>818.3161660963821</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q22" t="n">
-        <v>463.3441798078993</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>81.68251716755782</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S22" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="T22" t="n">
-        <v>163.0851070276585</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429943</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V22" t="n">
-        <v>448.1134299289403</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886177</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X22" t="n">
-        <v>610.6551392128113</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918435</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>608.2066695820797</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C23" t="n">
-        <v>476.4141663063283</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D23" t="n">
-        <v>384.1523928317325</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E23" t="n">
-        <v>297.9268477742895</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F23" t="n">
-        <v>211.169647059126</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G23" t="n">
-        <v>127.046419379738</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H23" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I23" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>141.6759849731407</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K23" t="n">
-        <v>790.1259849731551</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L23" t="n">
-        <v>1438.575984973169</v>
+        <v>1020.623267284697</v>
       </c>
       <c r="M23" t="n">
-        <v>1438.57598497317</v>
+        <v>1669.073267284701</v>
       </c>
       <c r="N23" t="n">
-        <v>1438.57598497317</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O23" t="n">
-        <v>1813.914800116309</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P23" t="n">
-        <v>2023.67004047503</v>
+        <v>2620</v>
       </c>
       <c r="Q23" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="R23" t="n">
-        <v>2620.000000000059</v>
+        <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2477.038452472669</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2213.182776293875</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.745133467757</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.754199965914</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
-        <v>1243.154729278088</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X23" t="n">
-        <v>967.1124732572119</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y23" t="n">
-        <v>772.8524402442762</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>502.7436970481501</v>
+        <v>1372.382356401963</v>
       </c>
       <c r="C24" t="n">
-        <v>460.218532961767</v>
+        <v>1104.66297740621</v>
       </c>
       <c r="D24" t="n">
-        <v>430.9885461964108</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E24" t="n">
-        <v>84.85511465912529</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F24" t="n">
-        <v>64.01042542894665</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G24" t="n">
-        <v>58.00018335964133</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H24" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="I24" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="J24" t="n">
-        <v>250.1913459300171</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K24" t="n">
-        <v>565.5796394772308</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L24" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M24" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N24" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O24" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P24" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q24" t="n">
-        <v>2313.990605368537</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2132.917892265886</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S24" t="n">
-        <v>1998.674143492789</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T24" t="n">
-        <v>1914.658037974812</v>
+        <v>1914.658037974811</v>
       </c>
       <c r="U24" t="n">
-        <v>1510.4576078759</v>
+        <v>1832.679830098122</v>
       </c>
       <c r="V24" t="n">
-        <v>1188.787971560955</v>
+        <v>1736.204408692546</v>
       </c>
       <c r="W24" t="n">
-        <v>1074.269645389411</v>
+        <v>1621.686082521002</v>
       </c>
       <c r="X24" t="n">
-        <v>650.165868171848</v>
+        <v>1519.804527525661</v>
       </c>
       <c r="Y24" t="n">
-        <v>568.9624411353487</v>
+        <v>1438.601100489161</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>673.4417775581356</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C25" t="n">
-        <v>719.2537833765714</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D25" t="n">
-        <v>752.3829275015714</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E25" t="n">
-        <v>790.0218317129844</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F25" t="n">
-        <v>834.1928043049199</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G25" t="n">
-        <v>908.0645554377069</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H25" t="n">
-        <v>1003.216333056121</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I25" t="n">
         <v>1163.862419205318</v>
       </c>
       <c r="J25" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K25" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L25" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M25" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N25" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O25" t="n">
-        <v>1109.635154952565</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P25" t="n">
-        <v>818.3161660963816</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q25" t="n">
-        <v>463.3441798078988</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R25" t="n">
-        <v>84.56167017509942</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S25" t="n">
-        <v>52.40000000000117</v>
+        <v>52.4</v>
       </c>
       <c r="T25" t="n">
-        <v>163.0851070276585</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U25" t="n">
-        <v>329.4820370429943</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V25" t="n">
-        <v>448.1134299289403</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W25" t="n">
-        <v>539.8143481886177</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X25" t="n">
-        <v>610.6551392128113</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y25" t="n">
-        <v>641.8744398918435</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="26">
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>607.5035534240307</v>
+        <v>607.5035534240907</v>
       </c>
       <c r="C26" t="n">
-        <v>475.7110501482792</v>
+        <v>475.7110501483393</v>
       </c>
       <c r="D26" t="n">
-        <v>383.4492766736835</v>
+        <v>383.4492766737435</v>
       </c>
       <c r="E26" t="n">
-        <v>297.2237316162404</v>
+        <v>297.2237316163004</v>
       </c>
       <c r="F26" t="n">
-        <v>211.1696470591254</v>
+        <v>210.4665309011369</v>
       </c>
       <c r="G26" t="n">
-        <v>127.0464193797374</v>
+        <v>126.3433032217489</v>
       </c>
       <c r="H26" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="I26" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="J26" t="n">
-        <v>141.67598497314</v>
+        <v>141.6759849731412</v>
       </c>
       <c r="K26" t="n">
-        <v>444.152717688452</v>
+        <v>790.1259849731629</v>
       </c>
       <c r="L26" t="n">
-        <v>674.6500000000099</v>
+        <v>1020.623267284721</v>
       </c>
       <c r="M26" t="n">
-        <v>1323.100000000016</v>
+        <v>1669.073267284728</v>
       </c>
       <c r="N26" t="n">
-        <v>1323.100000000016</v>
+        <v>2233.691587554895</v>
       </c>
       <c r="O26" t="n">
-        <v>1971.550000000022</v>
+        <v>2410.244759641367</v>
       </c>
       <c r="P26" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000088</v>
       </c>
       <c r="Q26" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000088</v>
       </c>
       <c r="R26" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000088</v>
       </c>
       <c r="S26" t="n">
-        <v>2476.33533631462</v>
+        <v>2476.33533631468</v>
       </c>
       <c r="T26" t="n">
-        <v>2212.479660135826</v>
+        <v>2212.479660135886</v>
       </c>
       <c r="U26" t="n">
-        <v>1879.042017309708</v>
+        <v>1879.042017309768</v>
       </c>
       <c r="V26" t="n">
-        <v>1565.051083807865</v>
+        <v>1565.051083807925</v>
       </c>
       <c r="W26" t="n">
-        <v>1242.451613120039</v>
+        <v>1242.451613120099</v>
       </c>
       <c r="X26" t="n">
-        <v>966.4093570991629</v>
+        <v>966.4093570992229</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.1493240862271</v>
+        <v>772.1493240862872</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>824.9659192703717</v>
+        <v>1050.160134179742</v>
       </c>
       <c r="C27" t="n">
-        <v>782.4407551839886</v>
+        <v>1007.634970093359</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964102</v>
+        <v>978.4049833280025</v>
       </c>
       <c r="E27" t="n">
-        <v>84.85511465912469</v>
+        <v>632.271551790717</v>
       </c>
       <c r="F27" t="n">
-        <v>64.01042542894604</v>
+        <v>611.4268625605383</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964073</v>
+        <v>283.1943982690108</v>
       </c>
       <c r="H27" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="I27" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="J27" t="n">
-        <v>250.1913459300165</v>
+        <v>250.1913459300177</v>
       </c>
       <c r="K27" t="n">
-        <v>565.5796394772301</v>
+        <v>565.5796394772312</v>
       </c>
       <c r="L27" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.61549399696</v>
       </c>
       <c r="M27" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739819</v>
       </c>
       <c r="N27" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.246884215312</v>
       </c>
       <c r="O27" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861295</v>
       </c>
       <c r="P27" t="n">
-        <v>2313.990605368536</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="Q27" t="n">
-        <v>2313.990605368536</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="R27" t="n">
-        <v>2132.917892265885</v>
+        <v>2132.917892265886</v>
       </c>
       <c r="S27" t="n">
-        <v>1998.674143492788</v>
+        <v>1998.674143492789</v>
       </c>
       <c r="T27" t="n">
         <v>1914.658037974812</v>
       </c>
       <c r="U27" t="n">
-        <v>1832.679830098122</v>
+        <v>1832.679830098123</v>
       </c>
       <c r="V27" t="n">
-        <v>1736.204408692546</v>
+        <v>1736.204408692547</v>
       </c>
       <c r="W27" t="n">
-        <v>1621.686082521002</v>
+        <v>1621.686082521003</v>
       </c>
       <c r="X27" t="n">
-        <v>1294.610312616292</v>
+        <v>1519.804527525662</v>
       </c>
       <c r="Y27" t="n">
-        <v>1213.406885579793</v>
+        <v>1438.601100489163</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.441777558135</v>
+        <v>673.4417775581362</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765707</v>
+        <v>719.253783376572</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015707</v>
+        <v>752.382927501572</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129837</v>
+        <v>790.021831712985</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049193</v>
+        <v>834.1928043049205</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377062</v>
+        <v>908.0645554377074</v>
       </c>
       <c r="H28" t="n">
-        <v>1003.21633305612</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205319</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K28" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794639</v>
       </c>
       <c r="L28" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928857</v>
       </c>
       <c r="M28" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291077</v>
       </c>
       <c r="N28" t="n">
-        <v>1342.719034054161</v>
+        <v>1339.83988104662</v>
       </c>
       <c r="O28" t="n">
-        <v>1112.514307960107</v>
+        <v>1109.635154952566</v>
       </c>
       <c r="P28" t="n">
-        <v>821.1953191039231</v>
+        <v>818.3161660963825</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154402</v>
+        <v>463.3441798078997</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017509878</v>
+        <v>84.56167017509998</v>
       </c>
       <c r="S28" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="T28" t="n">
-        <v>163.0851070276579</v>
+        <v>163.0851070276591</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370429937</v>
+        <v>329.4820370429949</v>
       </c>
       <c r="V28" t="n">
-        <v>448.1134299289396</v>
+        <v>448.1134299289408</v>
       </c>
       <c r="W28" t="n">
-        <v>539.814348188617</v>
+        <v>539.8143481886183</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128106</v>
+        <v>610.6551392128118</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918428</v>
+        <v>641.8744398918441</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>607.5035534240307</v>
+        <v>607.5035534240543</v>
       </c>
       <c r="C29" t="n">
-        <v>475.7110501482792</v>
+        <v>475.7110501483029</v>
       </c>
       <c r="D29" t="n">
-        <v>383.4492766736835</v>
+        <v>383.4492766737071</v>
       </c>
       <c r="E29" t="n">
-        <v>297.2237316162404</v>
+        <v>297.223731616264</v>
       </c>
       <c r="F29" t="n">
-        <v>210.4665309010769</v>
+        <v>210.4665309011006</v>
       </c>
       <c r="G29" t="n">
-        <v>127.0464193797374</v>
+        <v>127.0464193797386</v>
       </c>
       <c r="H29" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="I29" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="J29" t="n">
-        <v>288.3415875548099</v>
+        <v>141.6759849731412</v>
       </c>
       <c r="K29" t="n">
-        <v>936.7915875548167</v>
+        <v>327.4727226113322</v>
       </c>
       <c r="L29" t="n">
-        <v>1585.241587554824</v>
+        <v>936.7915875548401</v>
       </c>
       <c r="M29" t="n">
-        <v>2233.691587554835</v>
+        <v>1585.241587554849</v>
       </c>
       <c r="N29" t="n">
-        <v>2233.691587554835</v>
+        <v>2233.691587554858</v>
       </c>
       <c r="O29" t="n">
-        <v>2410.244759641307</v>
+        <v>2410.244759641331</v>
       </c>
       <c r="P29" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000051</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000051</v>
       </c>
       <c r="R29" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000051</v>
       </c>
       <c r="S29" t="n">
-        <v>2476.33533631462</v>
+        <v>2476.335336314643</v>
       </c>
       <c r="T29" t="n">
-        <v>2212.479660135826</v>
+        <v>2212.479660135849</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.042017309708</v>
+        <v>1879.042017309731</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.051083807865</v>
+        <v>1565.051083807889</v>
       </c>
       <c r="W29" t="n">
-        <v>1242.451613120039</v>
+        <v>1242.451613120063</v>
       </c>
       <c r="X29" t="n">
-        <v>966.4093570991629</v>
+        <v>966.4093570991865</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.1493240862271</v>
+        <v>772.1493240862508</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>502.7436970481496</v>
+        <v>1372.382356401964</v>
       </c>
       <c r="C30" t="n">
-        <v>137.9963107395442</v>
+        <v>1007.634970093359</v>
       </c>
       <c r="D30" t="n">
-        <v>108.766323974188</v>
+        <v>656.1827611057804</v>
       </c>
       <c r="E30" t="n">
-        <v>84.85511465912469</v>
+        <v>310.0493295684949</v>
       </c>
       <c r="F30" t="n">
-        <v>64.01042542894604</v>
+        <v>289.2046403383163</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964072</v>
+        <v>283.1943982690109</v>
       </c>
       <c r="H30" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="I30" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="J30" t="n">
-        <v>250.1913459300165</v>
+        <v>250.1913459300177</v>
       </c>
       <c r="K30" t="n">
-        <v>565.5796394772301</v>
+        <v>565.5796394772312</v>
       </c>
       <c r="L30" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.61549399696</v>
       </c>
       <c r="M30" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739819</v>
       </c>
       <c r="N30" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.246884215312</v>
       </c>
       <c r="O30" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861295</v>
       </c>
       <c r="P30" t="n">
-        <v>2313.990605368536</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="Q30" t="n">
-        <v>2313.990605368536</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="R30" t="n">
-        <v>2132.917892265885</v>
+        <v>2132.917892265886</v>
       </c>
       <c r="S30" t="n">
-        <v>1998.674143492788</v>
+        <v>1998.674143492789</v>
       </c>
       <c r="T30" t="n">
         <v>1914.658037974812</v>
       </c>
       <c r="U30" t="n">
-        <v>1607.485615188753</v>
+        <v>1832.679830098123</v>
       </c>
       <c r="V30" t="n">
-        <v>1511.010193783177</v>
+        <v>1736.204408692547</v>
       </c>
       <c r="W30" t="n">
-        <v>1074.269645389411</v>
+        <v>1621.686082521003</v>
       </c>
       <c r="X30" t="n">
-        <v>650.1658681718475</v>
+        <v>1519.804527525662</v>
       </c>
       <c r="Y30" t="n">
-        <v>568.9624411353482</v>
+        <v>1438.601100489163</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.441777558135</v>
+        <v>673.4417775581362</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765707</v>
+        <v>719.253783376572</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015707</v>
+        <v>752.382927501572</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129837</v>
+        <v>790.021831712985</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049193</v>
+        <v>834.1928043049205</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377062</v>
+        <v>908.0645554377074</v>
       </c>
       <c r="H31" t="n">
-        <v>1003.21633305612</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205319</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K31" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794639</v>
       </c>
       <c r="L31" t="n">
-        <v>1591.155096928856</v>
+        <v>1594.0342499364</v>
       </c>
       <c r="M31" t="n">
-        <v>1492.275360291076</v>
+        <v>1495.154513298619</v>
       </c>
       <c r="N31" t="n">
-        <v>1339.839881046619</v>
+        <v>1342.719034054162</v>
       </c>
       <c r="O31" t="n">
-        <v>1109.635154952565</v>
+        <v>1112.514307960108</v>
       </c>
       <c r="P31" t="n">
-        <v>818.3161660963812</v>
+        <v>821.1953191039242</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154402</v>
+        <v>466.2233328154414</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017509881</v>
+        <v>84.56167017510001</v>
       </c>
       <c r="S31" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="T31" t="n">
-        <v>163.0851070276579</v>
+        <v>163.0851070276591</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370429937</v>
+        <v>329.4820370429949</v>
       </c>
       <c r="V31" t="n">
-        <v>448.1134299289396</v>
+        <v>448.1134299289408</v>
       </c>
       <c r="W31" t="n">
-        <v>539.814348188617</v>
+        <v>539.8143481886183</v>
       </c>
       <c r="X31" t="n">
-        <v>610.6551392128106</v>
+        <v>610.6551392128118</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918428</v>
+        <v>641.8744398918441</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>608.2066695820791</v>
+        <v>607.5035534240907</v>
       </c>
       <c r="C32" t="n">
-        <v>476.4141663063277</v>
+        <v>475.7110501483393</v>
       </c>
       <c r="D32" t="n">
-        <v>384.152392831732</v>
+        <v>383.4492766737435</v>
       </c>
       <c r="E32" t="n">
-        <v>297.9268477742889</v>
+        <v>297.2237316163004</v>
       </c>
       <c r="F32" t="n">
-        <v>211.1696470591254</v>
+        <v>210.4665309011369</v>
       </c>
       <c r="G32" t="n">
-        <v>127.0464193797374</v>
+        <v>127.0464193797386</v>
       </c>
       <c r="H32" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="I32" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="J32" t="n">
-        <v>567.6776741934351</v>
+        <v>141.6759849731412</v>
       </c>
       <c r="K32" t="n">
-        <v>753.4744118316261</v>
+        <v>790.1259849731629</v>
       </c>
       <c r="L32" t="n">
-        <v>983.9716941431838</v>
+        <v>1020.623267284721</v>
       </c>
       <c r="M32" t="n">
-        <v>1146.546827913526</v>
+        <v>1669.073267284743</v>
       </c>
       <c r="N32" t="n">
-        <v>1794.996827913541</v>
+        <v>2233.691587554895</v>
       </c>
       <c r="O32" t="n">
-        <v>1971.550000000013</v>
+        <v>2410.244759641367</v>
       </c>
       <c r="P32" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000088</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620.000000000028</v>
+        <v>2620.000000000088</v>
       </c>
       <c r="R32" t="n">
-        <v>2620.000000000117</v>
+        <v>2620.000000000088</v>
       </c>
       <c r="S32" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.33533631468</v>
       </c>
       <c r="T32" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135886</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.042017309768</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.754199965914</v>
+        <v>1565.051083807925</v>
       </c>
       <c r="W32" t="n">
-        <v>1243.154729278088</v>
+        <v>1242.451613120099</v>
       </c>
       <c r="X32" t="n">
-        <v>967.1124732572114</v>
+        <v>966.4093570992229</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.8524402442756</v>
+        <v>772.1493240862872</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>727.9379119575187</v>
+        <v>502.7436970481507</v>
       </c>
       <c r="C33" t="n">
-        <v>685.4127478711356</v>
+        <v>137.9963107395454</v>
       </c>
       <c r="D33" t="n">
-        <v>656.1827611057794</v>
+        <v>108.7663239741891</v>
       </c>
       <c r="E33" t="n">
-        <v>310.0493295684939</v>
+        <v>84.85511465912589</v>
       </c>
       <c r="F33" t="n">
-        <v>64.01042542894604</v>
+        <v>64.01042542894723</v>
       </c>
       <c r="G33" t="n">
-        <v>58.00018335964073</v>
+        <v>58.00018335964192</v>
       </c>
       <c r="H33" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="I33" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="J33" t="n">
-        <v>250.1913459300165</v>
+        <v>250.1913459300177</v>
       </c>
       <c r="K33" t="n">
-        <v>565.5796394772301</v>
+        <v>565.5796394772312</v>
       </c>
       <c r="L33" t="n">
-        <v>1006.615493996959</v>
+        <v>1006.61549399696</v>
       </c>
       <c r="M33" t="n">
-        <v>1290.710885739818</v>
+        <v>1290.710885739819</v>
       </c>
       <c r="N33" t="n">
-        <v>1627.246884215311</v>
+        <v>1627.246884215312</v>
       </c>
       <c r="O33" t="n">
-        <v>2052.228604861294</v>
+        <v>2052.228604861295</v>
       </c>
       <c r="P33" t="n">
-        <v>2313.990605368536</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368536</v>
+        <v>2313.990605368537</v>
       </c>
       <c r="R33" t="n">
-        <v>1810.695670043663</v>
+        <v>2132.917892265886</v>
       </c>
       <c r="S33" t="n">
-        <v>1676.451921270566</v>
+        <v>1998.674143492789</v>
       </c>
       <c r="T33" t="n">
-        <v>1592.435815752589</v>
+        <v>1914.658037974812</v>
       </c>
       <c r="U33" t="n">
-        <v>1510.4576078759</v>
+        <v>1832.679830098123</v>
       </c>
       <c r="V33" t="n">
-        <v>1091.759964248102</v>
+        <v>1736.204408692547</v>
       </c>
       <c r="W33" t="n">
-        <v>977.2416380765576</v>
+        <v>1396.491867611634</v>
       </c>
       <c r="X33" t="n">
-        <v>875.3600830812167</v>
+        <v>972.3880903940708</v>
       </c>
       <c r="Y33" t="n">
-        <v>794.1566560447174</v>
+        <v>891.1846633575715</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.441777558135</v>
+        <v>673.4417775581362</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765707</v>
+        <v>719.253783376572</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015707</v>
+        <v>752.382927501572</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129837</v>
+        <v>790.021831712985</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049193</v>
+        <v>834.1928043049205</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377062</v>
+        <v>908.0645554377074</v>
       </c>
       <c r="H34" t="n">
-        <v>1003.21633305612</v>
+        <v>1003.216333056121</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205319</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743016</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794639</v>
       </c>
       <c r="L34" t="n">
-        <v>1591.155096928856</v>
+        <v>1591.155096928857</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291077</v>
       </c>
       <c r="N34" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.83988104662</v>
       </c>
       <c r="O34" t="n">
-        <v>1109.635154952565</v>
+        <v>1109.635154952566</v>
       </c>
       <c r="P34" t="n">
-        <v>821.1953191039231</v>
+        <v>818.3161660963821</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154402</v>
+        <v>463.3441798078993</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017509878</v>
+        <v>84.56167017510001</v>
       </c>
       <c r="S34" t="n">
-        <v>52.40000000000055</v>
+        <v>52.40000000000175</v>
       </c>
       <c r="T34" t="n">
-        <v>163.0851070276579</v>
+        <v>163.0851070276591</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370429937</v>
+        <v>329.4820370429949</v>
       </c>
       <c r="V34" t="n">
-        <v>448.1134299289396</v>
+        <v>448.1134299289408</v>
       </c>
       <c r="W34" t="n">
-        <v>539.814348188617</v>
+        <v>539.8143481886183</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128106</v>
+        <v>610.6551392128118</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918428</v>
+        <v>641.8744398918441</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113.8065837270021</v>
+        <v>117.1408562629495</v>
       </c>
       <c r="C35" t="n">
-        <v>60.80195923912946</v>
+        <v>64.13623177507688</v>
       </c>
       <c r="D35" t="n">
-        <v>47.3280645524125</v>
+        <v>50.66233708835992</v>
       </c>
       <c r="E35" t="n">
-        <v>39.89039828284821</v>
+        <v>43.22467081879563</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25534889150858</v>
+        <v>35.25534889151093</v>
       </c>
       <c r="G35" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="H35" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I35" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731389</v>
+        <v>119.1959849731412</v>
       </c>
       <c r="K35" t="n">
-        <v>489.4559849731312</v>
+        <v>304.9927226113322</v>
       </c>
       <c r="L35" t="n">
-        <v>719.9532672846891</v>
+        <v>535.49000492289</v>
       </c>
       <c r="M35" t="n">
-        <v>719.9532672846891</v>
+        <v>905.7500049229332</v>
       </c>
       <c r="N35" t="n">
-        <v>1090.213267284725</v>
+        <v>1109.691587554895</v>
       </c>
       <c r="O35" t="n">
-        <v>1286.24475964144</v>
+        <v>1286.244759641367</v>
       </c>
       <c r="P35" t="n">
-        <v>1496.00000000016</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="Q35" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R35" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="S35" t="n">
-        <v>1431.12321510244</v>
+        <v>1434.457487638387</v>
       </c>
       <c r="T35" t="n">
-        <v>1246.055417711524</v>
+        <v>1249.389690247472</v>
       </c>
       <c r="U35" t="n">
-        <v>991.4056536732851</v>
+        <v>994.7399262092325</v>
       </c>
       <c r="V35" t="n">
-        <v>756.2025989593216</v>
+        <v>759.536871495269</v>
       </c>
       <c r="W35" t="n">
-        <v>512.3910070593745</v>
+        <v>515.7252795953219</v>
       </c>
       <c r="X35" t="n">
-        <v>315.1366298263767</v>
+        <v>318.4709023623242</v>
       </c>
       <c r="Y35" t="n">
-        <v>199.6644756013198</v>
+        <v>202.9987481372672</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>372.9869114524003</v>
+        <v>1070.572551977267</v>
       </c>
       <c r="C36" t="n">
-        <v>372.9869114524003</v>
+        <v>1070.572551977267</v>
       </c>
       <c r="D36" t="n">
-        <v>372.9869114524003</v>
+        <v>719.1203429896882</v>
       </c>
       <c r="E36" t="n">
-        <v>372.9869114524003</v>
+        <v>372.9869114524027</v>
       </c>
       <c r="F36" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="G36" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="H36" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I36" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J36" t="n">
-        <v>227.7113459300153</v>
+        <v>227.7113459300177</v>
       </c>
       <c r="K36" t="n">
-        <v>543.0996394772289</v>
+        <v>543.0996394772313</v>
       </c>
       <c r="L36" t="n">
-        <v>599.9270509017573</v>
+        <v>599.9270509017597</v>
       </c>
       <c r="M36" t="n">
-        <v>863.9779994928817</v>
+        <v>599.9270509017597</v>
       </c>
       <c r="N36" t="n">
-        <v>863.9779994928817</v>
+        <v>936.4630493772524</v>
       </c>
       <c r="O36" t="n">
-        <v>1234.237999492918</v>
+        <v>1234.237999492845</v>
       </c>
       <c r="P36" t="n">
-        <v>1496.00000000016</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="Q36" t="n">
-        <v>1496.00000000016</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R36" t="n">
-        <v>1393.715165685388</v>
+        <v>1393.715165685315</v>
       </c>
       <c r="S36" t="n">
-        <v>1338.25929570017</v>
+        <v>1157.91832225362</v>
       </c>
       <c r="T36" t="n">
-        <v>1333.031068970072</v>
+        <v>1152.690095523522</v>
       </c>
       <c r="U36" t="n">
-        <v>1329.840739881261</v>
+        <v>1149.499766434712</v>
       </c>
       <c r="V36" t="n">
-        <v>1130.95801525665</v>
+        <v>1131.812223817014</v>
       </c>
       <c r="W36" t="n">
-        <v>753.1802374788355</v>
+        <v>1096.081776433349</v>
       </c>
       <c r="X36" t="n">
-        <v>375.4024597010209</v>
+        <v>1072.988100225887</v>
       </c>
       <c r="Y36" t="n">
-        <v>372.9869114524003</v>
+        <v>1070.572551977267</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="C37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="D37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="E37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="F37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="G37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="H37" t="n">
-        <v>817.3938833471308</v>
+        <v>679.5121617227951</v>
       </c>
       <c r="I37" t="n">
-        <v>1055.259969496328</v>
+        <v>917.3782478719928</v>
       </c>
       <c r="J37" t="n">
-        <v>1066.665307034026</v>
+        <v>928.78358540969</v>
       </c>
       <c r="K37" t="n">
-        <v>1066.665307034026</v>
+        <v>995.5392815331802</v>
       </c>
       <c r="L37" t="n">
-        <v>1066.665307034026</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="M37" t="n">
-        <v>1046.573449184124</v>
+        <v>1046.573449184127</v>
       </c>
       <c r="N37" t="n">
-        <v>972.9258487275459</v>
+        <v>972.9258487275482</v>
       </c>
       <c r="O37" t="n">
-        <v>821.5090014213708</v>
+        <v>821.5090014213731</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530661</v>
+        <v>608.9778913530683</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.793783852462</v>
+        <v>332.7937838524643</v>
       </c>
       <c r="R37" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="S37" t="n">
-        <v>75.61834706138561</v>
+        <v>75.61834706138796</v>
       </c>
       <c r="T37" t="n">
-        <v>263.523454089043</v>
+        <v>263.5234540890453</v>
       </c>
       <c r="U37" t="n">
-        <v>507.1403841043788</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="V37" t="n">
-        <v>702.9917769903248</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="W37" t="n">
-        <v>702.9917769903248</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="X37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
       <c r="Y37" t="n">
-        <v>817.3938833471308</v>
+        <v>507.1403841043811</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113.8065837270021</v>
+        <v>117.1408562629495</v>
       </c>
       <c r="C38" t="n">
-        <v>60.80195923912946</v>
+        <v>64.13623177507689</v>
       </c>
       <c r="D38" t="n">
-        <v>47.3280645524125</v>
+        <v>50.66233708835994</v>
       </c>
       <c r="E38" t="n">
-        <v>39.89039828284821</v>
+        <v>43.22467081879565</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889150858</v>
+        <v>35.25534889151095</v>
       </c>
       <c r="G38" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="H38" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I38" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J38" t="n">
-        <v>359.9280220030024</v>
+        <v>119.1959849731412</v>
       </c>
       <c r="K38" t="n">
-        <v>545.7247596411934</v>
+        <v>304.9927226113322</v>
       </c>
       <c r="L38" t="n">
-        <v>915.9847596411856</v>
+        <v>535.49000492289</v>
       </c>
       <c r="M38" t="n">
-        <v>915.9847596411856</v>
+        <v>905.7500049229584</v>
       </c>
       <c r="N38" t="n">
-        <v>915.9847596411856</v>
+        <v>1109.691587554895</v>
       </c>
       <c r="O38" t="n">
-        <v>1286.244759641249</v>
+        <v>1286.244759641367</v>
       </c>
       <c r="P38" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="Q38" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R38" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="S38" t="n">
-        <v>1431.12321510244</v>
+        <v>1431.123215102558</v>
       </c>
       <c r="T38" t="n">
-        <v>1246.055417711524</v>
+        <v>1246.055417711643</v>
       </c>
       <c r="U38" t="n">
-        <v>991.4056536732851</v>
+        <v>994.7399262092325</v>
       </c>
       <c r="V38" t="n">
-        <v>756.2025989593216</v>
+        <v>759.536871495269</v>
       </c>
       <c r="W38" t="n">
-        <v>512.3910070593745</v>
+        <v>515.7252795953219</v>
       </c>
       <c r="X38" t="n">
-        <v>315.1366298263767</v>
+        <v>318.4709023623242</v>
       </c>
       <c r="Y38" t="n">
-        <v>199.6644756013198</v>
+        <v>202.9987481372672</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>908.866195029448</v>
+        <v>1177.869556493014</v>
       </c>
       <c r="C39" t="n">
-        <v>544.1188087208427</v>
+        <v>813.1221701844081</v>
       </c>
       <c r="D39" t="n">
-        <v>357.7424055818618</v>
+        <v>461.6699611968297</v>
       </c>
       <c r="E39" t="n">
-        <v>357.7424055818618</v>
+        <v>115.5365296595442</v>
       </c>
       <c r="F39" t="n">
-        <v>357.7424055818618</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="G39" t="n">
-        <v>357.7424055818618</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="H39" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I39" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J39" t="n">
-        <v>29.91999999999938</v>
+        <v>227.7113459300177</v>
       </c>
       <c r="K39" t="n">
-        <v>345.308293547213</v>
+        <v>543.0996394772313</v>
       </c>
       <c r="L39" t="n">
-        <v>715.5682935472761</v>
+        <v>599.9270509017597</v>
       </c>
       <c r="M39" t="n">
-        <v>999.6636852901354</v>
+        <v>863.9779994927767</v>
       </c>
       <c r="N39" t="n">
-        <v>1188.111259659638</v>
+        <v>863.9779994927767</v>
       </c>
       <c r="O39" t="n">
-        <v>1234.237999492726</v>
+        <v>1234.237999492845</v>
       </c>
       <c r="P39" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="Q39" t="n">
-        <v>1495.999999999969</v>
+        <v>1422.956031069358</v>
       </c>
       <c r="R39" t="n">
-        <v>1393.715165685197</v>
+        <v>1320.671196754585</v>
       </c>
       <c r="S39" t="n">
-        <v>1338.259295699979</v>
+        <v>1265.215326769367</v>
       </c>
       <c r="T39" t="n">
-        <v>1333.031068969881</v>
+        <v>1259.987100039269</v>
       </c>
       <c r="U39" t="n">
-        <v>1329.84073988107</v>
+        <v>1256.796770950458</v>
       </c>
       <c r="V39" t="n">
-        <v>1312.153197263373</v>
+        <v>1239.109228332761</v>
       </c>
       <c r="W39" t="n">
-        <v>934.3754194855308</v>
+        <v>1203.378780949096</v>
       </c>
       <c r="X39" t="n">
-        <v>911.2817432780686</v>
+        <v>1180.285104741634</v>
       </c>
       <c r="Y39" t="n">
-        <v>908.866195029448</v>
+        <v>1177.869556493014</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>434.5620154974083</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="C40" t="n">
-        <v>434.5620154974083</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="D40" t="n">
-        <v>544.9111596224084</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="E40" t="n">
-        <v>544.9111596224084</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="F40" t="n">
-        <v>666.3021322143438</v>
+        <v>286.167443266348</v>
       </c>
       <c r="G40" t="n">
-        <v>817.3938833471308</v>
+        <v>286.167443266348</v>
       </c>
       <c r="H40" t="n">
-        <v>817.3938833471308</v>
+        <v>458.5392208847619</v>
       </c>
       <c r="I40" t="n">
-        <v>1055.259969496328</v>
+        <v>696.4053070339596</v>
       </c>
       <c r="J40" t="n">
-        <v>1066.665307034026</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="K40" t="n">
-        <v>1066.665307034026</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="L40" t="n">
-        <v>1066.665307034026</v>
+        <v>1066.665307034028</v>
       </c>
       <c r="M40" t="n">
-        <v>1046.573449184124</v>
+        <v>1046.573449184127</v>
       </c>
       <c r="N40" t="n">
-        <v>972.9258487275459</v>
+        <v>972.9258487275482</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213708</v>
+        <v>821.5090014213731</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530661</v>
+        <v>608.9778913530683</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.793783852462</v>
+        <v>332.7937838524644</v>
       </c>
       <c r="R40" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="S40" t="n">
-        <v>75.61834706138561</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="T40" t="n">
-        <v>75.61834706138561</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="U40" t="n">
-        <v>319.2352770767214</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="V40" t="n">
-        <v>319.2352770767214</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="W40" t="n">
-        <v>319.2352770767214</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="X40" t="n">
-        <v>434.5620154974083</v>
+        <v>164.7764706744125</v>
       </c>
       <c r="Y40" t="n">
-        <v>434.5620154974083</v>
+        <v>164.7764706744125</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>519.8967462380316</v>
+        <v>143.2836621243278</v>
       </c>
       <c r="C41" t="n">
-        <v>361.8416166996539</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="D41" t="n">
-        <v>243.3172169624319</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="E41" t="n">
-        <v>130.8290456423625</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="F41" t="n">
-        <v>130.8290456423625</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="G41" t="n">
-        <v>130.8290456423625</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="H41" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I41" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J41" t="n">
-        <v>119.1959849731389</v>
+        <v>119.1959849731412</v>
       </c>
       <c r="K41" t="n">
-        <v>489.4559849731312</v>
+        <v>304.9927226113322</v>
       </c>
       <c r="L41" t="n">
-        <v>719.9532672846891</v>
+        <v>535.49000492289</v>
       </c>
       <c r="M41" t="n">
-        <v>739.4315875546824</v>
+        <v>535.49000492289</v>
       </c>
       <c r="N41" t="n">
-        <v>739.4315875546824</v>
+        <v>578.9268279133773</v>
       </c>
       <c r="O41" t="n">
-        <v>915.9847596411551</v>
+        <v>755.47999999985</v>
       </c>
       <c r="P41" t="n">
-        <v>1125.739999999875</v>
+        <v>1125.739999999969</v>
       </c>
       <c r="Q41" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R41" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="S41" t="n">
-        <v>1326.072710051935</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="T41" t="n">
-        <v>1326.072710051935</v>
+        <v>1205.881697558667</v>
       </c>
       <c r="U41" t="n">
-        <v>1326.072710051935</v>
+        <v>1205.881697558667</v>
       </c>
       <c r="V41" t="n">
-        <v>1326.072710051935</v>
+        <v>1205.881697558667</v>
       </c>
       <c r="W41" t="n">
-        <v>977.2106131014827</v>
+        <v>857.0196006082153</v>
       </c>
       <c r="X41" t="n">
-        <v>740.4194055135936</v>
+        <v>554.7147183247125</v>
       </c>
       <c r="Y41" t="n">
-        <v>519.8967462380316</v>
+        <v>334.1920590491505</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.6172324016837</v>
+        <v>315.6172324016861</v>
       </c>
       <c r="C42" t="n">
-        <v>246.8294420526743</v>
+        <v>246.8294420526767</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290246918</v>
+        <v>191.3368290246942</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470023</v>
+        <v>141.1629934470047</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795419739</v>
+        <v>94.05567795419977</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962226582</v>
+        <v>61.7828096222682</v>
       </c>
       <c r="H42" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I42" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J42" t="n">
-        <v>227.7113459300153</v>
+        <v>227.7113459300177</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772289</v>
+        <v>250.1782010228479</v>
       </c>
       <c r="L42" t="n">
-        <v>913.3596394773226</v>
+        <v>620.4382010229668</v>
       </c>
       <c r="M42" t="n">
-        <v>913.3596394773226</v>
+        <v>904.5335927658261</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.111259659638</v>
+        <v>1241.069591241319</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999492726</v>
+        <v>1451.197204214989</v>
       </c>
       <c r="P42" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="Q42" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R42" t="n">
-        <v>1286.253778366616</v>
+        <v>1286.253778366618</v>
       </c>
       <c r="S42" t="n">
-        <v>1125.747403330892</v>
+        <v>1125.747403330895</v>
       </c>
       <c r="T42" t="n">
-        <v>1015.46867155029</v>
+        <v>1015.468671550292</v>
       </c>
       <c r="U42" t="n">
-        <v>907.2278374109738</v>
+        <v>907.2278374109762</v>
       </c>
       <c r="V42" t="n">
-        <v>784.4897897427717</v>
+        <v>784.4897897427741</v>
       </c>
       <c r="W42" t="n">
-        <v>643.7088373086015</v>
+        <v>643.7088373086038</v>
       </c>
       <c r="X42" t="n">
-        <v>515.5646560506342</v>
+        <v>515.5646560506366</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515086</v>
+        <v>408.098602751511</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.7817775581337</v>
+        <v>470.7817775581361</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765695</v>
+        <v>490.8537833765719</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015696</v>
+        <v>498.242927501572</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129827</v>
+        <v>510.141831712985</v>
       </c>
       <c r="F43" t="n">
-        <v>528.5728043049181</v>
+        <v>528.5728043049205</v>
       </c>
       <c r="G43" t="n">
-        <v>576.704555437705</v>
+        <v>576.7045554377074</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561189</v>
+        <v>646.1163330561214</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053166</v>
+        <v>781.0224192053191</v>
       </c>
       <c r="J43" t="n">
-        <v>1082.497756743014</v>
+        <v>1082.497756743016</v>
       </c>
       <c r="K43" t="n">
-        <v>1163.052803794636</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="L43" t="n">
-        <v>1130.572470666229</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="M43" t="n">
-        <v>1041.942907913439</v>
+        <v>1160.444850760474</v>
       </c>
       <c r="N43" t="n">
-        <v>1041.942907913439</v>
+        <v>981.7467452533908</v>
       </c>
       <c r="O43" t="n">
-        <v>785.4755555567591</v>
+        <v>725.2793928967108</v>
       </c>
       <c r="P43" t="n">
-        <v>785.4755555567591</v>
+        <v>407.6977777779009</v>
       </c>
       <c r="Q43" t="n">
-        <v>407.697777778373</v>
+        <v>407.6977777779009</v>
       </c>
       <c r="R43" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="S43" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="T43" t="n">
-        <v>114.8651070276567</v>
+        <v>114.8651070276591</v>
       </c>
       <c r="U43" t="n">
-        <v>255.5220370429925</v>
+        <v>255.5220370429949</v>
       </c>
       <c r="V43" t="n">
-        <v>348.4134299289385</v>
+        <v>348.4134299289408</v>
       </c>
       <c r="W43" t="n">
-        <v>414.3743481886158</v>
+        <v>414.3743481886182</v>
       </c>
       <c r="X43" t="n">
-        <v>459.4751392128094</v>
+        <v>459.4751392128118</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918416</v>
+        <v>464.954439891844</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>294.2243547524472</v>
+        <v>306.4995292756015</v>
       </c>
       <c r="C44" t="n">
-        <v>294.2243547524472</v>
+        <v>148.4443997372238</v>
       </c>
       <c r="D44" t="n">
-        <v>175.6999550152252</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="E44" t="n">
-        <v>130.8290456423625</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="F44" t="n">
-        <v>130.8290456423625</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="G44" t="n">
-        <v>130.8290456423625</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="H44" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="I44" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J44" t="n">
-        <v>119.1959849731389</v>
+        <v>119.1959849731412</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113298</v>
+        <v>489.4559849731629</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228876</v>
+        <v>719.9532672847208</v>
       </c>
       <c r="M44" t="n">
-        <v>905.75000492288</v>
+        <v>719.9532672847208</v>
       </c>
       <c r="N44" t="n">
-        <v>1109.691587554776</v>
+        <v>1090.213267284933</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.244759641249</v>
+        <v>1266.766439371406</v>
       </c>
       <c r="P44" t="n">
-        <v>1495.999999999969</v>
+        <v>1476.521679730126</v>
       </c>
       <c r="Q44" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R44" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="S44" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="T44" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="U44" t="n">
-        <v>1136.299730911225</v>
+        <v>1136.299730911343</v>
       </c>
       <c r="V44" t="n">
-        <v>1136.299730911225</v>
+        <v>796.0461711468748</v>
       </c>
       <c r="W44" t="n">
-        <v>787.4376339607727</v>
+        <v>447.1840741964227</v>
       </c>
       <c r="X44" t="n">
-        <v>485.1327516772699</v>
+        <v>447.1840741964227</v>
       </c>
       <c r="Y44" t="n">
-        <v>485.1327516772699</v>
+        <v>447.1840741964227</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>318.0281146697595</v>
+        <v>318.0281146698783</v>
       </c>
       <c r="C45" t="n">
-        <v>249.2403243207501</v>
+        <v>249.2403243208689</v>
       </c>
       <c r="D45" t="n">
-        <v>193.7477112927677</v>
+        <v>193.7477112928865</v>
       </c>
       <c r="E45" t="n">
-        <v>143.5738757150781</v>
+        <v>143.5738757151969</v>
       </c>
       <c r="F45" t="n">
-        <v>96.46656022227323</v>
+        <v>96.46656022239203</v>
       </c>
       <c r="G45" t="n">
-        <v>64.19369189034165</v>
+        <v>64.19369189046046</v>
       </c>
       <c r="H45" t="n">
-        <v>32.33088226807523</v>
+        <v>32.33088226819402</v>
       </c>
       <c r="I45" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="J45" t="n">
-        <v>227.7113459300153</v>
+        <v>227.7113459300177</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772289</v>
+        <v>250.1782010228479</v>
       </c>
       <c r="L45" t="n">
-        <v>863.9779994927342</v>
+        <v>620.4382010230604</v>
       </c>
       <c r="M45" t="n">
-        <v>863.9779994927342</v>
+        <v>904.5335927659196</v>
       </c>
       <c r="N45" t="n">
-        <v>863.9779994927342</v>
+        <v>1241.069591241412</v>
       </c>
       <c r="O45" t="n">
-        <v>1234.237999492726</v>
+        <v>1451.197204214989</v>
       </c>
       <c r="P45" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="Q45" t="n">
-        <v>1495.999999999969</v>
+        <v>1496.000000000088</v>
       </c>
       <c r="R45" t="n">
-        <v>1288.664660634692</v>
+        <v>1288.66466063481</v>
       </c>
       <c r="S45" t="n">
-        <v>1128.158285598968</v>
+        <v>1128.158285599087</v>
       </c>
       <c r="T45" t="n">
-        <v>1017.879553818365</v>
+        <v>1017.879553818484</v>
       </c>
       <c r="U45" t="n">
-        <v>909.6387196790497</v>
+        <v>909.6387196791685</v>
       </c>
       <c r="V45" t="n">
-        <v>786.9006720108475</v>
+        <v>786.9006720109663</v>
       </c>
       <c r="W45" t="n">
-        <v>646.1197195766773</v>
+        <v>646.1197195767961</v>
       </c>
       <c r="X45" t="n">
-        <v>517.9755383187101</v>
+        <v>517.9755383188289</v>
       </c>
       <c r="Y45" t="n">
-        <v>410.5094850195844</v>
+        <v>410.5094850197032</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>470.7817775581337</v>
+        <v>470.7817775581361</v>
       </c>
       <c r="C46" t="n">
-        <v>490.8537833765695</v>
+        <v>490.8537833765719</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2429275015696</v>
+        <v>498.242927501572</v>
       </c>
       <c r="E46" t="n">
-        <v>510.1418317129827</v>
+        <v>510.141831712985</v>
       </c>
       <c r="F46" t="n">
-        <v>528.5728043049181</v>
+        <v>528.5728043049205</v>
       </c>
       <c r="G46" t="n">
-        <v>576.704555437705</v>
+        <v>576.7045554377074</v>
       </c>
       <c r="H46" t="n">
-        <v>646.1163330561189</v>
+        <v>646.1163330561214</v>
       </c>
       <c r="I46" t="n">
-        <v>781.0224192053166</v>
+        <v>781.0224192053191</v>
       </c>
       <c r="J46" t="n">
-        <v>1082.497756743014</v>
+        <v>1082.497756743016</v>
       </c>
       <c r="K46" t="n">
-        <v>1163.052803794636</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="L46" t="n">
-        <v>1130.572470666229</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="M46" t="n">
-        <v>1130.572470666229</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="N46" t="n">
-        <v>951.8743651591453</v>
+        <v>1163.052803794639</v>
       </c>
       <c r="O46" t="n">
-        <v>783.7036893343038</v>
+        <v>1161.481467112525</v>
       </c>
       <c r="P46" t="n">
-        <v>466.1220742154939</v>
+        <v>843.8998519937156</v>
       </c>
       <c r="Q46" t="n">
-        <v>88.3442964377239</v>
+        <v>466.1220742157209</v>
       </c>
       <c r="R46" t="n">
-        <v>88.3442964377239</v>
+        <v>88.34429643772624</v>
       </c>
       <c r="S46" t="n">
-        <v>29.91999999999938</v>
+        <v>29.92000000000176</v>
       </c>
       <c r="T46" t="n">
-        <v>114.8651070276567</v>
+        <v>114.8651070276591</v>
       </c>
       <c r="U46" t="n">
-        <v>255.5220370429925</v>
+        <v>255.5220370429949</v>
       </c>
       <c r="V46" t="n">
-        <v>348.4134299289385</v>
+        <v>348.4134299289408</v>
       </c>
       <c r="W46" t="n">
-        <v>414.3743481886158</v>
+        <v>414.3743481886182</v>
       </c>
       <c r="X46" t="n">
-        <v>459.4751392128094</v>
+        <v>459.4751392128118</v>
       </c>
       <c r="Y46" t="n">
-        <v>464.9544398918416</v>
+        <v>464.954439891844</v>
       </c>
     </row>
   </sheetData>
@@ -7964,19 +7964,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2405037325275146</v>
+        <v>183.5817792952637</v>
       </c>
       <c r="K2" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>846.2608914614127</v>
       </c>
       <c r="N2" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O2" t="n">
         <v>1.159015302735668</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>374.2405037325275</v>
+        <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
         <v>321.8400703517588</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>235.5012052109774</v>
       </c>
       <c r="M5" t="n">
-        <v>472.2608914614128</v>
+        <v>846.2608914614127</v>
       </c>
       <c r="N5" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
         <v>1.159015302735668</v>
       </c>
       <c r="P5" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8441,7 +8441,7 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -8450,13 +8450,13 @@
         <v>846.2608914614127</v>
       </c>
       <c r="N8" t="n">
-        <v>404.0826666125488</v>
+        <v>778.0826666125488</v>
       </c>
       <c r="O8" t="n">
-        <v>1.159015302735668</v>
+        <v>184.5002908654719</v>
       </c>
       <c r="P8" t="n">
-        <v>235.5012052109774</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>502.5418702571336</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -8684,19 +8684,19 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>846.1834570112101</v>
+        <v>290.1886884942145</v>
       </c>
       <c r="N11" t="n">
-        <v>868.9937721402016</v>
+        <v>868.993772140187</v>
       </c>
       <c r="O11" t="n">
-        <v>476.6634625389312</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8915,22 +8915,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L14" t="n">
-        <v>117.8585808859859</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>940.1988562855481</v>
+        <v>940.1988562855336</v>
       </c>
       <c r="N14" t="n">
-        <v>213.993772140187</v>
+        <v>784.3153077665602</v>
       </c>
       <c r="O14" t="n">
-        <v>476.6634625389312</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>443.1260198396911</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>13.49857879984722</v>
@@ -9152,16 +9152,16 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>467.3265276382056</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>382.6480632645622</v>
       </c>
       <c r="M17" t="n">
-        <v>855.5203919119358</v>
+        <v>940.1988562855347</v>
       </c>
       <c r="N17" t="n">
-        <v>868.9937721402016</v>
+        <v>868.9937721401884</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9389,25 +9389,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>467.3265276382056</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855356</v>
       </c>
       <c r="N20" t="n">
-        <v>213.993772140187</v>
+        <v>821.3370988185927</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>443.1260198396766</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>365.3893580004311</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,25 +9626,25 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>467.3265276382056</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L23" t="n">
-        <v>422.1744623115724</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>285.1988562855334</v>
+        <v>940.1988562855374</v>
       </c>
       <c r="N23" t="n">
-        <v>213.993772140187</v>
+        <v>784.3153077665565</v>
       </c>
       <c r="O23" t="n">
-        <v>200.7935788451181</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,22 +9863,22 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>117.8585808859808</v>
+        <v>467.3265276382128</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855395</v>
+        <v>940.1988562855408</v>
       </c>
       <c r="N26" t="n">
-        <v>213.993772140187</v>
+        <v>784.3153077666182</v>
       </c>
       <c r="O26" t="n">
-        <v>476.6634625389225</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>443.1260198396825</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>13.49857879984722</v>
@@ -10097,19 +10097,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>148.1470733148181</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>467.3265276381979</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>422.1744623115647</v>
+        <v>382.6480632645961</v>
       </c>
       <c r="M29" t="n">
-        <v>940.1988562855447</v>
+        <v>940.1988562855427</v>
       </c>
       <c r="N29" t="n">
-        <v>213.993772140187</v>
+        <v>868.9937721401961</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>467.3265276382128</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>449.416163124263</v>
+        <v>940.1988562855554</v>
       </c>
       <c r="N32" t="n">
-        <v>868.9937721402016</v>
+        <v>784.3153077666034</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>443.1260198396911</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
         <v>13.49857879984722</v>
@@ -10574,25 +10574,25 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>186.3265276381832</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>285.1988562855334</v>
+        <v>659.1988562855772</v>
       </c>
       <c r="N35" t="n">
-        <v>587.9937721402234</v>
+        <v>419.9953707583301</v>
       </c>
       <c r="O35" t="n">
-        <v>19.67507098004265</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>13.49857879965407</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10659,13 +10659,13 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>451.4479081556279</v>
+        <v>184.7297782656032</v>
       </c>
       <c r="N36" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O36" t="n">
-        <v>327.4073335019674</v>
+        <v>254.190111396469</v>
       </c>
       <c r="P36" t="n">
         <v>219.1507118405495</v>
@@ -10808,22 +10808,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>243.1636737675389</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
         <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>141.17446231155</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>285.1988562855334</v>
+        <v>659.1988562856027</v>
       </c>
       <c r="N38" t="n">
-        <v>213.993772140187</v>
+        <v>419.9953707583046</v>
       </c>
       <c r="O38" t="n">
-        <v>195.6634625389803</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -10887,22 +10887,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>27.675503614641</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
         <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>316.598574318722</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>471.6948204301074</v>
+        <v>451.4479081555193</v>
       </c>
       <c r="N39" t="n">
-        <v>335.8242603976229</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>327.4073335020001</v>
       </c>
       <c r="P39" t="n">
         <v>219.1507118405495</v>
@@ -11048,25 +11048,25 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>186.3265276381832</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>304.8739272653247</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N41" t="n">
-        <v>213.993772140187</v>
+        <v>257.8693509184571</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>162.1260198397965</v>
       </c>
       <c r="Q41" t="n">
-        <v>387.4985787999419</v>
+        <v>387.4985787999674</v>
       </c>
       <c r="R41" t="n">
         <v>294.54111633436</v>
@@ -11127,22 +11127,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K42" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>316.5985743187529</v>
+        <v>316.5985743187784</v>
       </c>
       <c r="M42" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>423.000064248949</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>165.6574476167494</v>
       </c>
       <c r="P42" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
         <v>17.27519534353338</v>
@@ -11285,16 +11285,16 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>186.3265276382129</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>659.1988562855256</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>419.9953707582639</v>
+        <v>587.9937721404017</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -11303,7 +11303,7 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>13.49857879984722</v>
+        <v>33.1736497796062</v>
       </c>
       <c r="R44" t="n">
         <v>294.54111633436</v>
@@ -11364,22 +11364,22 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>266.7181298898757</v>
+        <v>316.598574318873</v>
       </c>
       <c r="M45" t="n">
-        <v>184.7297782656032</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N45" t="n">
-        <v>145.473175175903</v>
+        <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>327.4073335019232</v>
+        <v>165.657447616655</v>
       </c>
       <c r="P45" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6960849964379605</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.696084996495216</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23420,13 +23420,13 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.850361477466606</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -23475,7 +23475,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.6960849964948983</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -23523,7 +23523,7 @@
         <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.6960849964379463</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.850361477466162</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23712,10 +23712,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.696084996437998</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.6960849964948608</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23894,7 +23894,7 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.850361477465711</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.696084996437998</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -23997,7 +23997,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.850361477466162</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24186,7 +24186,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6960849964380316</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24377,10 +24377,10 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.850361477466549</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24420,13 +24420,13 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.6960849964680023</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.6960849964097662</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.850361477466112</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24614,7 +24614,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.850361477466265</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -24660,7 +24660,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6960849964679454</v>
+        <v>0.6960849964457339</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.850361477466802</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24848,7 +24848,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.850361477466436</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -24897,7 +24897,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.6960849964097235</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -24933,7 +24933,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.6960849963799376</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>0</v>
@@ -25082,13 +25082,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.850361477466038</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.850361477466663</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>3.300929810585617</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.300929810470514</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.300929810585617</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.300929810470478</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25593,16 +25593,16 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>44.24455273991111</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>111.8896287080119</v>
@@ -25611,7 +25611,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25644,10 +25644,10 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>168.2280170485541</v>
       </c>
       <c r="T41" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>356.1032663978569</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>64.85853794865744</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25781,25 +25781,25 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M43" t="n">
-        <v>36.14767214614074</v>
+        <v>121.3090657675793</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>314.4057989676218</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.422266424995769</v>
+        <v>377.422266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>29.84504601334811</v>
+        <v>29.84504601381779</v>
       </c>
       <c r="S43" t="n">
         <v>57.84005347334724</v>
@@ -25830,16 +25830,16 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>49.72161348396151</v>
       </c>
       <c r="C44" t="n">
-        <v>156.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>66.94108932773456</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
         <v>111.8896287080119</v>
@@ -25848,7 +25848,7 @@
         <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>99.89995518593948</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25890,13 +25890,13 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>218.3174326828064</v>
@@ -26018,25 +26018,25 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>32.15552979712344</v>
       </c>
       <c r="M46" t="n">
         <v>123.8909392714024</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O46" t="n">
-        <v>87.41370976652024</v>
+        <v>252.3470555178209</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.422266425605699</v>
+        <v>3.422266425383242</v>
       </c>
       <c r="R46" t="n">
-        <v>403.8450460139379</v>
+        <v>29.8450460137232</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4503284.975280119</v>
+        <v>4503284.975280114</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5605131.545660112</v>
+        <v>5605131.545660103</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6706978.116040102</v>
+        <v>6706978.11604009</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7808824.68642009</v>
+        <v>7808824.686420074</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8910671.256800078</v>
+        <v>8910671.256800057</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10012517.82718006</v>
+        <v>10012517.82718005</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11114364.39756005</v>
+        <v>11114364.39756004</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12216210.96794005</v>
+        <v>12216210.96794003</v>
       </c>
     </row>
     <row r="13">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15370480.02292384</v>
+        <v>15370480.02292385</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16358090.18038383</v>
+        <v>16358090.18038386</v>
       </c>
     </row>
   </sheetData>
@@ -26272,46 +26272,46 @@
         <v>1101954.91029102</v>
       </c>
       <c r="C2" t="n">
-        <v>1101954.910291021</v>
+        <v>1101954.91029102</v>
       </c>
       <c r="D2" t="n">
         <v>1101954.91029102</v>
       </c>
       <c r="E2" t="n">
-        <v>1101846.570379992</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="F2" t="n">
+        <v>1101846.570379988</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1101846.570379988</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1101846.570379988</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1101846.570379988</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1101846.570379994</v>
+      </c>
+      <c r="K2" t="n">
         <v>1101846.570379991</v>
       </c>
-      <c r="G2" t="n">
-        <v>1101846.570379992</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1101846.570379992</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1101846.570379992</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1101846.57037999</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1101846.57037999</v>
-      </c>
       <c r="L2" t="n">
-        <v>1101846.570379996</v>
+        <v>1101846.570379994</v>
       </c>
       <c r="M2" t="n">
-        <v>1101725.000529713</v>
+        <v>1101725.000529722</v>
       </c>
       <c r="N2" t="n">
-        <v>1101725.000529714</v>
+        <v>1101725.000529722</v>
       </c>
       <c r="O2" t="n">
-        <v>987610.157459986</v>
+        <v>987610.157459994</v>
       </c>
       <c r="P2" t="n">
-        <v>987610.1574599855</v>
+        <v>987610.157459994</v>
       </c>
     </row>
     <row r="3">
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>612487.0000000051</v>
+        <v>612487</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386847.9999999972</v>
+        <v>386848.0000000077</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101187</v>
+        <v>602219.8615549037</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.6066068059</v>
+        <v>598199.291951591</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685821</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687451</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731246</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963690008</v>
+        <v>503256.5379432671</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285019</v>
+        <v>501580.9146027683</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045224</v>
+        <v>499902.9383787917</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.7505265506</v>
+        <v>498222.592100819</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963799</v>
+        <v>496539.8583706453</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842124</v>
+        <v>522371.0444804655</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.330873149</v>
+        <v>520403.9137694004</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844155927</v>
+        <v>447670.967311844</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523472</v>
+        <v>446003.2126485987</v>
       </c>
     </row>
     <row r="5">
@@ -26434,40 +26434,40 @@
         <v>58590.39999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>74642.61100000089</v>
+        <v>74642.611</v>
       </c>
       <c r="F5" t="n">
-        <v>74642.61100000089</v>
+        <v>74642.611</v>
       </c>
       <c r="G5" t="n">
-        <v>74642.61100000089</v>
+        <v>74642.611</v>
       </c>
       <c r="H5" t="n">
-        <v>74642.61100000089</v>
+        <v>74642.611</v>
       </c>
       <c r="I5" t="n">
-        <v>74642.61100000089</v>
+        <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.61100000043</v>
+        <v>74642.61100000134</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.61100000043</v>
+        <v>74642.61100000134</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.61100000043</v>
+        <v>74642.61100000134</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.19299999953</v>
+        <v>64115.19300000134</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.19299999953</v>
+        <v>64115.19300000134</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01699999953</v>
+        <v>55372.01700000133</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01699999953</v>
+        <v>55372.01700000133</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209847.3340809016</v>
+        <v>210046.6487361166</v>
       </c>
       <c r="C6" t="n">
-        <v>442954.2562683906</v>
+        <v>443153.5709236051</v>
       </c>
       <c r="D6" t="n">
-        <v>444965.9036842143</v>
+        <v>445165.218339429</v>
       </c>
       <c r="E6" t="n">
-        <v>-93746.65808859635</v>
+        <v>-93552.4996628605</v>
       </c>
       <c r="F6" t="n">
-        <v>520409.0074112453</v>
+        <v>520603.1658369763</v>
       </c>
       <c r="G6" t="n">
-        <v>522079.9756068665</v>
+        <v>522274.1340325965</v>
       </c>
       <c r="H6" t="n">
-        <v>523753.26301099</v>
+        <v>523947.4214367206</v>
       </c>
       <c r="I6" t="n">
-        <v>525428.8863514889</v>
+        <v>525623.0447772193</v>
       </c>
       <c r="J6" t="n">
-        <v>140258.8625754696</v>
+        <v>140453.0210011931</v>
       </c>
       <c r="K6" t="n">
-        <v>528787.2088534387</v>
+        <v>528981.3672791708</v>
       </c>
       <c r="L6" t="n">
-        <v>530469.9425836155</v>
+        <v>530664.101009347</v>
       </c>
       <c r="M6" t="n">
-        <v>452719.3459455016</v>
+        <v>452838.763049255</v>
       </c>
       <c r="N6" t="n">
-        <v>517086.4766565652</v>
+        <v>517205.89376032</v>
       </c>
       <c r="O6" t="n">
-        <v>312447.7560443938</v>
+        <v>312567.1731481486</v>
       </c>
       <c r="P6" t="n">
-        <v>486115.5107076387</v>
+        <v>486234.927811394</v>
       </c>
     </row>
   </sheetData>
@@ -26868,40 +26868,40 @@
         <v>374</v>
       </c>
       <c r="E4" t="n">
-        <v>655.0000000000147</v>
+        <v>655</v>
       </c>
       <c r="F4" t="n">
-        <v>655.0000000000147</v>
+        <v>655</v>
       </c>
       <c r="G4" t="n">
-        <v>655.0000000000147</v>
+        <v>655</v>
       </c>
       <c r="H4" t="n">
-        <v>655.0000000000147</v>
+        <v>655</v>
       </c>
       <c r="I4" t="n">
-        <v>655.0000000000147</v>
+        <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655.0000000000069</v>
+        <v>655.0000000000219</v>
       </c>
       <c r="K4" t="n">
-        <v>655.0000000000069</v>
+        <v>655.0000000000219</v>
       </c>
       <c r="L4" t="n">
-        <v>655.0000000000069</v>
+        <v>655.0000000000219</v>
       </c>
       <c r="M4" t="n">
-        <v>373.9999999999923</v>
+        <v>374.0000000000219</v>
       </c>
       <c r="N4" t="n">
-        <v>373.9999999999923</v>
+        <v>374.0000000000219</v>
       </c>
       <c r="O4" t="n">
-        <v>373.9999999999923</v>
+        <v>374.0000000000219</v>
       </c>
       <c r="P4" t="n">
-        <v>373.9999999999923</v>
+        <v>374.0000000000219</v>
       </c>
     </row>
   </sheetData>
@@ -26990,7 +26990,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
         <v>-0</v>
@@ -27008,7 +27008,7 @@
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>281.0000000000076</v>
+        <v>281</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>373.9999999999993</v>
+        <v>374.0000000000147</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>281.0000000000147</v>
+        <v>281</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>132.4740095033003</v>
+        <v>134.2726973711268</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>225.120779732817</v>
+        <v>223.3220918649904</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27521,7 +27521,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -27533,7 +27533,7 @@
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>167.7850168218854</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27563,7 +27563,7 @@
         <v>400</v>
       </c>
       <c r="S3" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>399.3913927661343</v>
+        <v>77.42051134503032</v>
       </c>
     </row>
     <row r="4">
@@ -27606,10 +27606,10 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>400</v>
+        <v>227.1357818393235</v>
       </c>
       <c r="I4" t="n">
         <v>171.1020457840527</v>
@@ -27642,13 +27642,13 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>390.2336871679398</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
-        <v>209.2386648669134</v>
+        <v>390.9596374183397</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
         <v>400</v>
@@ -27660,7 +27660,7 @@
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27752,7 +27752,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
         <v>347.9376868977026</v>
@@ -27761,16 +27761,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>330.0491815260438</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>200.2217829794704</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,13 +27794,13 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
       </c>
       <c r="S6" t="n">
-        <v>88.48881128536601</v>
+        <v>400</v>
       </c>
       <c r="T6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>70.4523295467165</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27843,19 +27843,19 @@
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
         <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>171.1020457840527</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>396.2647849014816</v>
+        <v>62.9493556471818</v>
       </c>
       <c r="K7" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>396.2015953708939</v>
@@ -27879,13 +27879,13 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
-        <v>375.352003005331</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V7" t="n">
         <v>199.1703102162162</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>398.2013121321735</v>
       </c>
       <c r="I8" t="n">
         <v>134.2726973711268</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>223.3220918649904</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
         <v>400</v>
@@ -27989,10 +27989,10 @@
         <v>10.55655664632661</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>276.356946342818</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28001,7 +28001,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>246.9767472028209</v>
       </c>
       <c r="H9" t="n">
         <v>330.0491815260438</v>
@@ -28052,7 +28052,7 @@
         <v>400</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>45.86273944538755</v>
       </c>
       <c r="Y9" t="n">
         <v>25.39139276613435</v>
@@ -28071,25 +28071,25 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>285.5362180555555</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
         <v>400</v>
       </c>
       <c r="F10" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>244.8599384153005</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I10" t="n">
         <v>171.1020457840527</v>
       </c>
       <c r="J10" t="n">
-        <v>345.8437401624712</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K10" t="n">
         <v>267.1509377355693</v>
@@ -28122,10 +28122,10 @@
         <v>209.2386648669134</v>
       </c>
       <c r="U10" t="n">
-        <v>400</v>
+        <v>150.9483584875727</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>203.7157012675546</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28229,7 +28229,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>286.0053395461674</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>319</v>
@@ -28244,7 +28244,7 @@
         <v>319</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28271,13 +28271,13 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>319</v>
+        <v>96.05772723972422</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="U12" t="n">
         <v>319</v>
@@ -28289,7 +28289,7 @@
         <v>319</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y12" t="n">
         <v>319</v>
@@ -28460,22 +28460,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96.05772723972461</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>319</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F15" t="n">
         <v>319</v>
       </c>
       <c r="G15" t="n">
-        <v>319</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="H15" t="n">
         <v>319</v>
@@ -28529,7 +28529,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -28697,19 +28697,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="C18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G18" t="n">
         <v>319</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R18" t="n">
         <v>319</v>
@@ -28757,13 +28757,13 @@
         <v>319</v>
       </c>
       <c r="V18" t="n">
-        <v>168.3712564811476</v>
+        <v>319</v>
       </c>
       <c r="W18" t="n">
         <v>319</v>
       </c>
       <c r="X18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
         <v>319</v>
@@ -28779,7 +28779,7 @@
         <v>319</v>
       </c>
       <c r="C19" t="n">
-        <v>319.0000000000004</v>
+        <v>319</v>
       </c>
       <c r="D19" t="n">
         <v>319</v>
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>96.05772723972456</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>319</v>
@@ -28997,7 +28997,7 @@
         <v>319</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>96.0577272397241</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -29031,7 +29031,7 @@
         <v>319</v>
       </c>
       <c r="H22" t="n">
-        <v>319.0000000000001</v>
+        <v>319</v>
       </c>
       <c r="I22" t="n">
         <v>319</v>
@@ -29174,16 +29174,16 @@
         <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="D24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29228,16 +29228,16 @@
         <v>319</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V24" t="n">
-        <v>96.05772723972467</v>
+        <v>319</v>
       </c>
       <c r="W24" t="n">
         <v>319</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y24" t="n">
         <v>319</v>
@@ -29414,7 +29414,7 @@
         <v>319</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -29423,10 +29423,10 @@
         <v>319</v>
       </c>
       <c r="G27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>319</v>
+        <v>96.05772723972481</v>
       </c>
       <c r="I27" t="n">
         <v>189.9476123064429</v>
@@ -29474,7 +29474,7 @@
         <v>319</v>
       </c>
       <c r="X27" t="n">
-        <v>96.05772723972433</v>
+        <v>319</v>
       </c>
       <c r="Y27" t="n">
         <v>319</v>
@@ -29651,10 +29651,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>319</v>
@@ -29663,7 +29663,7 @@
         <v>319</v>
       </c>
       <c r="H30" t="n">
-        <v>319</v>
+        <v>96.05772723972464</v>
       </c>
       <c r="I30" t="n">
         <v>189.9476123064429</v>
@@ -29702,16 +29702,16 @@
         <v>319</v>
       </c>
       <c r="U30" t="n">
-        <v>96.05772723972433</v>
+        <v>319</v>
       </c>
       <c r="V30" t="n">
         <v>319</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="Y30" t="n">
         <v>319</v>
@@ -29851,7 +29851,7 @@
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>158.2009556123023</v>
+        <v>158.200955612214</v>
       </c>
       <c r="S32" t="n">
         <v>319</v>
@@ -29882,19 +29882,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
         <v>319</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F33" t="n">
-        <v>96.0577272397245</v>
+        <v>319</v>
       </c>
       <c r="G33" t="n">
         <v>319</v>
@@ -29930,7 +29930,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="S33" t="n">
         <v>319</v>
@@ -29942,13 +29942,13 @@
         <v>319</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W33" t="n">
-        <v>319</v>
+        <v>96.05772723972456</v>
       </c>
       <c r="X33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
         <v>319</v>
@@ -30125,10 +30125,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
@@ -30170,7 +30170,7 @@
         <v>397</v>
       </c>
       <c r="S36" t="n">
-        <v>397</v>
+        <v>218.4624362879874</v>
       </c>
       <c r="T36" t="n">
         <v>397</v>
@@ -30179,13 +30179,13 @@
         <v>397</v>
       </c>
       <c r="V36" t="n">
-        <v>217.616769813155</v>
+        <v>397</v>
       </c>
       <c r="W36" t="n">
-        <v>58.37314290979211</v>
+        <v>397</v>
       </c>
       <c r="X36" t="n">
-        <v>45.86273944535114</v>
+        <v>397</v>
       </c>
       <c r="Y36" t="n">
         <v>397</v>
@@ -30216,7 +30216,7 @@
         <v>244.3820695628415</v>
       </c>
       <c r="H37" t="n">
-        <v>222.8870933147334</v>
+        <v>397</v>
       </c>
       <c r="I37" t="n">
         <v>397</v>
@@ -30225,10 +30225,10 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>211.6312656044217</v>
+        <v>279.0612616887553</v>
       </c>
       <c r="L37" t="n">
-        <v>325.1555297971234</v>
+        <v>397</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30258,13 +30258,13 @@
         <v>397</v>
       </c>
       <c r="V37" t="n">
-        <v>397</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>363.0013286188005</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
         <v>287.4653528494624</v>
@@ -30362,19 +30362,19 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>163.4250477901116</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>254.8758779749299</v>
       </c>
       <c r="G39" t="n">
         <v>324.9501396486123</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
         <v>189.9476123064429</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>397</v>
@@ -30419,7 +30419,7 @@
         <v>397</v>
       </c>
       <c r="W39" t="n">
-        <v>58.37314290976482</v>
+        <v>397</v>
       </c>
       <c r="X39" t="n">
         <v>397</v>
@@ -30441,7 +30441,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>397</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E40" t="n">
         <v>280.9809048369565</v>
@@ -30450,16 +30450,16 @@
         <v>397</v>
       </c>
       <c r="G40" t="n">
+        <v>244.3820695628415</v>
+      </c>
+      <c r="H40" t="n">
         <v>397</v>
-      </c>
-      <c r="H40" t="n">
-        <v>222.8870933147334</v>
       </c>
       <c r="I40" t="n">
         <v>397</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>362.4794570326982</v>
       </c>
       <c r="K40" t="n">
         <v>211.6312656044217</v>
@@ -30486,22 +30486,22 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>397</v>
+        <v>350.8400534733473</v>
       </c>
       <c r="T40" t="n">
         <v>207.1968615882249</v>
       </c>
       <c r="U40" t="n">
-        <v>397</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V40" t="n">
-        <v>199.1703102162162</v>
+        <v>335.3889674630957</v>
       </c>
       <c r="W40" t="n">
         <v>226.3728098387097</v>
       </c>
       <c r="X40" t="n">
-        <v>363.9353004004984</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y40" t="n">
         <v>287.4653528494624</v>
@@ -30641,7 +30641,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R42" t="n">
-        <v>290.6132265546047</v>
+        <v>290.6132265544897</v>
       </c>
       <c r="S42" t="n">
         <v>293</v>
@@ -30851,7 +30851,7 @@
         <v>293</v>
       </c>
       <c r="I45" t="n">
-        <v>187.5608388610478</v>
+        <v>187.5608388609326</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -34743,19 +34743,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="K2" t="n">
-        <v>374</v>
+        <v>52.15992964824122</v>
       </c>
       <c r="L2" t="n">
-        <v>300.210210236103</v>
+        <v>64.70900502512563</v>
       </c>
       <c r="M2" t="n">
         <v>374</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -34892,10 +34892,10 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>155.1400615846995</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>172.8642181606765</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -34928,13 +34928,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>31.06568287492044</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>181.7209725514263</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
         <v>200.8296897837838</v>
@@ -34946,7 +34946,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
         <v>374</v>
       </c>
-      <c r="K5" t="n">
-        <v>373.9999999999999</v>
-      </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>300.210210236103</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>294.1798838637633</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35129,19 +35129,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
         <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J7" t="n">
-        <v>374</v>
+        <v>40.68457074570026</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,13 +35165,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698065</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>224.4036445177583</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -35220,22 +35220,22 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L8" t="n">
-        <v>64.70900502512563</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M8" t="n">
         <v>374</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="P8" t="n">
-        <v>294.1798838637633</v>
+        <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
         <v>374</v>
@@ -35357,25 +35357,25 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
         <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>323.5789552609896</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35408,10 +35408,10 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0516415124273</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>4.545391051338353</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35454,7 +35454,7 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K11" t="n">
         <v>187.6734723618091</v>
@@ -35463,19 +35463,19 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M11" t="n">
-        <v>560.9846007256767</v>
+        <v>4.989832208681115</v>
       </c>
       <c r="N11" t="n">
-        <v>655.0000000000147</v>
+        <v>655.0000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>655.0000000000147</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P11" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35694,22 +35694,22 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K14" t="n">
-        <v>187.6734723618091</v>
+        <v>655</v>
       </c>
       <c r="L14" t="n">
-        <v>350.6841185744281</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M14" t="n">
-        <v>655.0000000000147</v>
+        <v>655.0000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>570.3215356263732</v>
       </c>
       <c r="O14" t="n">
-        <v>655.0000000000147</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P14" t="n">
-        <v>655.0000000000147</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35931,16 +35931,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K17" t="n">
-        <v>655.0000000000147</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L17" t="n">
-        <v>232.8255376884422</v>
+        <v>615.4736009530044</v>
       </c>
       <c r="M17" t="n">
-        <v>570.3215356264025</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="N17" t="n">
-        <v>655.0000000000147</v>
+        <v>655.0000000000013</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
@@ -36065,7 +36065,7 @@
         <v>31.88619966292134</v>
       </c>
       <c r="C19" t="n">
-        <v>46.27475335195572</v>
+        <v>46.27475335195533</v>
       </c>
       <c r="D19" t="n">
         <v>33.46378194444452</v>
@@ -36089,7 +36089,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K19" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -36168,25 +36168,25 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K20" t="n">
-        <v>655.0000000000147</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L20" t="n">
         <v>232.8255376884422</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>655.0000000000022</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>607.3433266784056</v>
       </c>
       <c r="O20" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P20" t="n">
-        <v>655.0000000000001</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q20" t="n">
-        <v>351.8907792005839</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36317,7 +36317,7 @@
         <v>74.61793043715849</v>
       </c>
       <c r="H22" t="n">
-        <v>96.11290668526667</v>
+        <v>96.11290668526664</v>
       </c>
       <c r="I22" t="n">
         <v>162.2687738880785</v>
@@ -36405,25 +36405,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K23" t="n">
-        <v>655.0000000000147</v>
+        <v>655</v>
       </c>
       <c r="L23" t="n">
-        <v>655.0000000000146</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>655.000000000004</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>570.3215356263696</v>
       </c>
       <c r="O23" t="n">
-        <v>379.1301163062016</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P23" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q23" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36642,22 +36642,22 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K26" t="n">
-        <v>305.5320532477899</v>
+        <v>655.0000000000219</v>
       </c>
       <c r="L26" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M26" t="n">
-        <v>655.000000000006</v>
+        <v>655.0000000000074</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>570.3215356264311</v>
       </c>
       <c r="O26" t="n">
-        <v>655.000000000006</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P26" t="n">
-        <v>655.000000000006</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -36876,19 +36876,19 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>238.3248359139489</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K29" t="n">
-        <v>655.0000000000069</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L29" t="n">
-        <v>655.0000000000069</v>
+        <v>615.4736009530384</v>
       </c>
       <c r="M29" t="n">
-        <v>655.0000000000113</v>
+        <v>655.0000000000092</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>655.0000000000092</v>
       </c>
       <c r="O29" t="n">
         <v>178.3365374610834</v>
@@ -37113,25 +37113,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
-        <v>187.673472361809</v>
+        <v>655.0000000000219</v>
       </c>
       <c r="L32" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M32" t="n">
-        <v>164.2173068387296</v>
+        <v>655.0000000000219</v>
       </c>
       <c r="N32" t="n">
-        <v>655.0000000000147</v>
+        <v>570.3215356264164</v>
       </c>
       <c r="O32" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P32" t="n">
-        <v>655.0000000000147</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37274,7 +37274,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K34" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -37353,25 +37353,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K35" t="n">
-        <v>373.9999999999923</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>374.0000000000437</v>
       </c>
       <c r="N35" t="n">
-        <v>374.0000000000364</v>
+        <v>206.0015986181431</v>
       </c>
       <c r="O35" t="n">
-        <v>198.0116084411261</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P35" t="n">
         <v>211.8739801603236</v>
       </c>
       <c r="Q35" t="n">
-        <v>-1.931527889371295e-10</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37438,13 +37438,13 @@
         <v>57.40142568134173</v>
       </c>
       <c r="M36" t="n">
-        <v>266.7181298900247</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O36" t="n">
-        <v>374.0000000000364</v>
+        <v>300.7827778945381</v>
       </c>
       <c r="P36" t="n">
         <v>264.4060611184268</v>
@@ -37502,7 +37502,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I37" t="n">
         <v>240.2687738880785</v>
@@ -37511,10 +37511,10 @@
         <v>11.52054296737091</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>67.42999608433357</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>71.84447020287655</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,7 +37535,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>46.15994652665276</v>
+        <v>46.15994652665273</v>
       </c>
       <c r="T37" t="n">
         <v>189.8031384117751</v>
@@ -37544,13 +37544,13 @@
         <v>246.0777070861978</v>
       </c>
       <c r="V37" t="n">
-        <v>197.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>115.557683188693</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
         <v>0</v>
@@ -37587,22 +37587,22 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>333.3414363666697</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K38" t="n">
         <v>187.673472361809</v>
       </c>
       <c r="L38" t="n">
-        <v>373.9999999999923</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>206.0015986181176</v>
       </c>
       <c r="O38" t="n">
-        <v>374.0000000000637</v>
+        <v>178.3365374610834</v>
       </c>
       <c r="P38" t="n">
         <v>211.8739801603236</v>
@@ -37666,22 +37666,22 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K39" t="n">
         <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>374.0000000000637</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M39" t="n">
-        <v>286.9650421645043</v>
+        <v>266.7181298899162</v>
       </c>
       <c r="N39" t="n">
-        <v>190.3510852217199</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>46.59266649806909</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="P39" t="n">
         <v>264.4060611184268</v>
@@ -37727,7 +37727,7 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>111.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -37736,16 +37736,16 @@
         <v>122.6171440322581</v>
       </c>
       <c r="G40" t="n">
-        <v>152.6179304371585</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I40" t="n">
         <v>240.2687738880785</v>
       </c>
       <c r="J40" t="n">
-        <v>11.52054296737091</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -37772,22 +37772,22 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>46.15994652665276</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>136.2186572468795</v>
       </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>116.4916549703908</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
@@ -37827,25 +37827,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K41" t="n">
-        <v>373.9999999999923</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884423</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M41" t="n">
-        <v>19.67507097979124</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>43.87557877827008</v>
       </c>
       <c r="O41" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P41" t="n">
-        <v>211.8739801603236</v>
+        <v>374.0000000001201</v>
       </c>
       <c r="Q41" t="n">
-        <v>374.0000000000946</v>
+        <v>374.0000000001201</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -37906,22 +37906,22 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K42" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L42" t="n">
-        <v>374.0000000000946</v>
+        <v>374.0000000001201</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>277.5268890730459</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O42" t="n">
-        <v>46.59266649806909</v>
+        <v>212.2501141148184</v>
       </c>
       <c r="P42" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
@@ -38064,16 +38064,16 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K44" t="n">
-        <v>187.673472361809</v>
+        <v>374.0000000000219</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M44" t="n">
-        <v>373.9999999999923</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>206.0015986180769</v>
+        <v>374.0000000002147</v>
       </c>
       <c r="O44" t="n">
         <v>178.3365374610834</v>
@@ -38082,7 +38082,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>19.67507097975898</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
@@ -38143,22 +38143,22 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K45" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L45" t="n">
-        <v>324.1195555712174</v>
+        <v>374.0000000002147</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
-        <v>373.9999999999923</v>
+        <v>212.250114114724</v>
       </c>
       <c r="P45" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -38216,13 +38216,13 @@
         <v>70.11290668526664</v>
       </c>
       <c r="I46" t="n">
-        <v>136.2687738880785</v>
+        <v>136.2687738880784</v>
       </c>
       <c r="J46" t="n">
         <v>304.5205429673709</v>
       </c>
       <c r="K46" t="n">
-        <v>81.36873439557826</v>
+        <v>81.36873439557824</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -38249,7 +38249,7 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>85.80313841177508</v>
+        <v>85.80313841177507</v>
       </c>
       <c r="U46" t="n">
         <v>142.0777070861978</v>
